--- a/research/traditional_assets/database/data/israel/israel_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0757</v>
+        <v>0.05614999999999999</v>
       </c>
       <c r="E2">
-        <v>0.317</v>
+        <v>0.0646</v>
       </c>
       <c r="G2">
-        <v>0.1746234993654434</v>
+        <v>0.2703330074771432</v>
       </c>
       <c r="H2">
-        <v>0.1733456578701594</v>
+        <v>0.267589354194511</v>
       </c>
       <c r="I2">
-        <v>0.3441173030561709</v>
+        <v>0.393487502796899</v>
       </c>
       <c r="J2">
-        <v>0.2920911530199715</v>
+        <v>0.3292117772715555</v>
       </c>
       <c r="K2">
-        <v>117.682</v>
+        <v>200.17</v>
       </c>
       <c r="L2">
-        <v>0.1027178571366226</v>
+        <v>0.2395102824180045</v>
       </c>
       <c r="M2">
-        <v>94.34428</v>
+        <v>62.06816</v>
       </c>
       <c r="N2">
-        <v>0.03276923985342387</v>
+        <v>0.03458028859546493</v>
       </c>
       <c r="O2">
-        <v>0.8016882785812613</v>
+        <v>0.3100772343508018</v>
       </c>
       <c r="P2">
-        <v>91.86427999999999</v>
+        <v>55.17416</v>
       </c>
       <c r="Q2">
-        <v>0.03190784460151786</v>
+        <v>0.03073940609504708</v>
       </c>
       <c r="R2">
-        <v>0.7806145374823676</v>
+        <v>0.2756365089673777</v>
       </c>
       <c r="S2">
-        <v>2.48</v>
+        <v>6.894</v>
       </c>
       <c r="T2">
-        <v>0.02628670227808194</v>
+        <v>0.1110714414604847</v>
       </c>
       <c r="U2">
-        <v>446.76</v>
+        <v>353.377</v>
       </c>
       <c r="V2">
-        <v>0.1551761865893263</v>
+        <v>0.1968783776254945</v>
       </c>
       <c r="W2">
-        <v>0.2386634844868735</v>
+        <v>0.01666001020548348</v>
       </c>
       <c r="X2">
-        <v>0.05272561695192858</v>
+        <v>0.08180431776258129</v>
       </c>
       <c r="Y2">
-        <v>0.185937867534945</v>
+        <v>-0.06514430755709781</v>
       </c>
       <c r="Z2">
-        <v>0.7455716952928093</v>
+        <v>0.3983537670602793</v>
       </c>
       <c r="AA2">
-        <v>0.1328906973729556</v>
+        <v>-0.002816630683234928</v>
       </c>
       <c r="AB2">
-        <v>0.04919288587961176</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC2">
-        <v>0.08237533071277019</v>
+        <v>-0.0835984881203108</v>
       </c>
       <c r="AD2">
-        <v>1379.934</v>
+        <v>1991.015</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1379.934</v>
+        <v>1991.015</v>
       </c>
       <c r="AG2">
-        <v>933.174</v>
+        <v>1637.638</v>
       </c>
       <c r="AH2">
-        <v>0.3240054435517954</v>
+        <v>0.5259006079111654</v>
       </c>
       <c r="AI2">
-        <v>0.4837270639307438</v>
+        <v>0.52872444528832</v>
       </c>
       <c r="AJ2">
-        <v>0.2447846716247524</v>
+        <v>0.4770924604476338</v>
       </c>
       <c r="AK2">
-        <v>0.3878606056978692</v>
+        <v>0.4799195151213925</v>
       </c>
       <c r="AL2">
-        <v>113.75</v>
+        <v>42.337</v>
       </c>
       <c r="AM2">
-        <v>101.548</v>
+        <v>0.2559999999999931</v>
       </c>
       <c r="AN2">
-        <v>4.82642911105515</v>
+        <v>8.841293101534225</v>
       </c>
       <c r="AO2">
-        <v>3.465925274725275</v>
+        <v>7.767579186054752</v>
       </c>
       <c r="AP2">
-        <v>3.263850415512465</v>
+        <v>7.272088634294722</v>
       </c>
       <c r="AQ2">
-        <v>3.882390593610904</v>
+        <v>1284.593750000035</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Keystone REIT Ltd. (TASE:KSTN)</t>
+          <t>Spring Ventures Ltd (TASE:SPRG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,23 +721,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.7390000000000001</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.8744186046511628</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.8643410852713178</v>
       </c>
       <c r="I3">
-        <v>0.1671009771986971</v>
+        <v>0.9147286821705427</v>
       </c>
       <c r="J3">
-        <v>0.1671009771986971</v>
+        <v>0.6977738024249652</v>
       </c>
       <c r="K3">
-        <v>-2.07</v>
+        <v>17.8</v>
       </c>
       <c r="L3">
-        <v>-0.6742671009771987</v>
+        <v>0.689922480620155</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,58 +758,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.7</v>
+        <v>2.48</v>
       </c>
       <c r="V3">
-        <v>0.1763070077864294</v>
+        <v>0.07272727272727272</v>
+      </c>
+      <c r="W3">
+        <v>0.4472361809045227</v>
       </c>
       <c r="X3">
-        <v>0.05502663066906462</v>
+        <v>0.07948470944208655</v>
+      </c>
+      <c r="Y3">
+        <v>0.3677514714624361</v>
+      </c>
+      <c r="Z3">
+        <v>0.683805989928439</v>
+      </c>
+      <c r="AA3">
+        <v>0.4771419057133344</v>
       </c>
       <c r="AB3">
-        <v>0.04995298779094625</v>
+        <v>0.0793831149959246</v>
+      </c>
+      <c r="AC3">
+        <v>0.3977587907174098</v>
       </c>
       <c r="AD3">
-        <v>42.5</v>
+        <v>0.114</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>42.5</v>
+        <v>0.114</v>
       </c>
       <c r="AG3">
-        <v>10.8</v>
+        <v>-2.366</v>
       </c>
       <c r="AH3">
-        <v>0.191183085919928</v>
+        <v>0.003331969369264044</v>
       </c>
       <c r="AI3">
-        <v>0.1927437641723356</v>
+        <v>0.002072199803686335</v>
       </c>
       <c r="AJ3">
-        <v>0.05666316894018887</v>
+        <v>-0.07455725720047898</v>
       </c>
       <c r="AK3">
-        <v>0.05720338983050847</v>
+        <v>-0.04503749952411772</v>
       </c>
       <c r="AL3">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.32</v>
-      </c>
-      <c r="AO3">
-        <v>0.3772058823529412</v>
+        <v>-0.002</v>
+      </c>
+      <c r="AN3">
+        <v>0.004810126582278481</v>
+      </c>
+      <c r="AP3">
+        <v>-0.09983122362869198</v>
       </c>
       <c r="AQ3">
-        <v>0.3886363636363636</v>
+        <v>-11800</v>
       </c>
     </row>
     <row r="4">
@@ -817,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Big Tech 50 R&amp;D-Limited Partnership (TASE:BIGT.L)</t>
+          <t>Keystone REIT Ltd. (TASE:KSTN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,91 +847,115 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.3371559633027523</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.3371559633027523</v>
       </c>
       <c r="I4">
-        <v>0.6361788617886178</v>
+        <v>0.9105504587155964</v>
       </c>
       <c r="J4">
-        <v>0.4789233993902439</v>
+        <v>0.6900584193853623</v>
       </c>
       <c r="K4">
-        <v>2.41</v>
+        <v>50.7</v>
       </c>
       <c r="L4">
-        <v>0.4898373983739838</v>
+        <v>0.5814220183486238</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>11.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08784313725490195</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2209072978303747</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>11.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.08784313725490195</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2209072978303747</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>9.550000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="V4">
-        <v>0.4483568075117371</v>
+        <v>0.2682352941176471</v>
+      </c>
+      <c r="W4">
+        <v>0.2848314606741573</v>
       </c>
       <c r="X4">
-        <v>0.04887865283753826</v>
+        <v>0.1593475256579594</v>
+      </c>
+      <c r="Y4">
+        <v>0.125483935016198</v>
+      </c>
+      <c r="Z4">
+        <v>0.461864406779661</v>
+      </c>
+      <c r="AA4">
+        <v>0.3187134225127308</v>
       </c>
       <c r="AB4">
-        <v>0.04887865283753826</v>
+        <v>0.07573575604237995</v>
+      </c>
+      <c r="AC4">
+        <v>0.2429776664703509</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>326.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>326.3</v>
       </c>
       <c r="AG4">
-        <v>-9.550000000000001</v>
+        <v>292.1</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.7190392243278978</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.4404103117829666</v>
       </c>
       <c r="AJ4">
-        <v>-0.8127659574468086</v>
+        <v>0.696139180171592</v>
       </c>
       <c r="AK4">
-        <v>1.341292134831461</v>
+        <v>0.4133295599264186</v>
       </c>
       <c r="AL4">
-        <v>0.082</v>
+        <v>9.44</v>
       </c>
       <c r="AM4">
-        <v>-0.07099999999999999</v>
+        <v>8.719999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>4.109571788413098</v>
       </c>
       <c r="AO4">
-        <v>38.17073170731707</v>
+        <v>8.411016949152543</v>
+      </c>
+      <c r="AP4">
+        <v>3.678841309823678</v>
       </c>
       <c r="AQ4">
-        <v>-44.08450704225352</v>
+        <v>9.105504587155965</v>
       </c>
     </row>
     <row r="5">
@@ -921,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unicorn Technologies - Limited Partnership (TASE:UNCT.L)</t>
+          <t>Y.D. More Investments Ltd (TASE:MRIN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -929,92 +974,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.283</v>
+      </c>
+      <c r="E5">
+        <v>0.194</v>
+      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.114828897338403</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.114828897338403</v>
       </c>
       <c r="I5">
-        <v>0.2282442748091603</v>
+        <v>0.1429657794676806</v>
       </c>
       <c r="J5">
-        <v>0.2282442748091603</v>
+        <v>0.08927915082382763</v>
       </c>
       <c r="K5">
-        <v>0.17</v>
+        <v>11.2</v>
       </c>
       <c r="L5">
-        <v>0.1297709923664122</v>
+        <v>0.08517110266159696</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>6.08</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.03210137275607181</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>6.08</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.03210137275607181</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>13</v>
+        <v>43.7</v>
       </c>
       <c r="V5">
-        <v>1.150442477876106</v>
+        <v>0.2307286166842661</v>
+      </c>
+      <c r="W5">
+        <v>0.3137254901960784</v>
       </c>
       <c r="X5">
-        <v>0.04887865283753826</v>
+        <v>0.0857813857808791</v>
+      </c>
+      <c r="Y5">
+        <v>0.2279441044151993</v>
+      </c>
+      <c r="Z5">
+        <v>2.543520309477756</v>
+      </c>
+      <c r="AA5">
+        <v>0.2270833333333334</v>
       </c>
       <c r="AB5">
-        <v>0.04887865283753826</v>
+        <v>0.07851845990929961</v>
+      </c>
+      <c r="AC5">
+        <v>0.1485648734240338</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="AG5">
-        <v>-13</v>
+        <v>-4.900000000000006</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.1700262927256792</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.3154471544715447</v>
       </c>
       <c r="AJ5">
-        <v>7.647058823529415</v>
+        <v>-0.02655826558265586</v>
       </c>
       <c r="AK5">
-        <v>-1.780821917808219</v>
+        <v>-0.06179066834804547</v>
       </c>
       <c r="AL5">
-        <v>0.162</v>
+        <v>1.13</v>
       </c>
       <c r="AM5">
-        <v>0.162</v>
+        <v>0.6339999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>1.911330049261084</v>
       </c>
       <c r="AO5">
-        <v>1.845679012345679</v>
+        <v>16.63716814159292</v>
+      </c>
+      <c r="AP5">
+        <v>-0.2413793103448278</v>
       </c>
       <c r="AQ5">
-        <v>1.845679012345679</v>
+        <v>29.65299684542587</v>
       </c>
     </row>
     <row r="6">
@@ -1025,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Altshuler Shaham Provident Funds and Pension Ltd (TASE:ASPF)</t>
+          <t>Generation Capital Ltd (TASE:GNRS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1034,40 +1109,40 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.1809571286141575</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.1809571286141575</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.2624626121635095</v>
+        <v>0.8797423049391554</v>
       </c>
       <c r="J6">
-        <v>0.1597249535796281</v>
+        <v>0.7026072936363775</v>
       </c>
       <c r="K6">
-        <v>71.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L6">
-        <v>0.1787138584247258</v>
+        <v>0.5934144595561919</v>
       </c>
       <c r="M6">
-        <v>26</v>
+        <v>15.18</v>
       </c>
       <c r="N6">
-        <v>0.02443838706645361</v>
+        <v>0.037060546875</v>
       </c>
       <c r="O6">
-        <v>0.3626220362622036</v>
+        <v>0.1831121833534379</v>
       </c>
       <c r="P6">
-        <v>26</v>
+        <v>15.18</v>
       </c>
       <c r="Q6">
-        <v>0.02443838706645361</v>
+        <v>0.037060546875</v>
       </c>
       <c r="R6">
-        <v>0.3626220362622036</v>
+        <v>0.1831121833534379</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1076,73 +1151,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>82.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="V6">
-        <v>0.07716890685214775</v>
+        <v>0.219970703125</v>
       </c>
       <c r="W6">
-        <v>0.9263565891472868</v>
+        <v>0.1667001809772773</v>
       </c>
       <c r="X6">
-        <v>0.0545944492053648</v>
+        <v>0.1108024970669028</v>
       </c>
       <c r="Y6">
-        <v>0.871762139941922</v>
+        <v>0.05589768391037454</v>
       </c>
       <c r="Z6">
-        <v>3.429059829059828</v>
+        <v>0.2534930139720559</v>
       </c>
       <c r="AA6">
-        <v>0.5477064220183485</v>
+        <v>0.1781060405026346</v>
       </c>
       <c r="AB6">
-        <v>0.04946840962529336</v>
+        <v>0.07683887368315701</v>
       </c>
       <c r="AC6">
-        <v>0.4982380123930552</v>
+        <v>0.1012671668194776</v>
       </c>
       <c r="AD6">
-        <v>233.8</v>
+        <v>411.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>233.8</v>
+        <v>411.9</v>
       </c>
       <c r="AG6">
-        <v>151.7</v>
+        <v>321.8</v>
       </c>
       <c r="AH6">
-        <v>0.1801649071434076</v>
+        <v>0.5013998782714546</v>
       </c>
       <c r="AI6">
-        <v>0.6298491379310345</v>
+        <v>0.4347229551451187</v>
       </c>
       <c r="AJ6">
-        <v>0.1247943402435012</v>
+        <v>0.4399781241454744</v>
       </c>
       <c r="AK6">
-        <v>0.5247319266689727</v>
+        <v>0.3753207371121997</v>
       </c>
       <c r="AL6">
-        <v>6.18</v>
+        <v>17.2</v>
       </c>
       <c r="AM6">
-        <v>6.18</v>
-      </c>
-      <c r="AN6">
-        <v>2.0875</v>
+        <v>16.966</v>
       </c>
       <c r="AO6">
-        <v>17.03883495145631</v>
-      </c>
-      <c r="AP6">
-        <v>1.354464285714286</v>
+        <v>7.145348837209303</v>
       </c>
       <c r="AQ6">
-        <v>17.03883495145631</v>
+        <v>7.243899563833551</v>
       </c>
     </row>
     <row r="7">
@@ -1153,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Y.D. More Investments Ltd (TASE:MRIN)</t>
+          <t>Capital Point Ltd. (TASE:CPTP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1161,116 +1230,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="E7">
+        <v>-0.0636</v>
+      </c>
       <c r="G7">
-        <v>0.09914255091103966</v>
+        <v>1.419558359621451</v>
       </c>
       <c r="H7">
-        <v>0.09914255091103966</v>
+        <v>1.419558359621451</v>
       </c>
       <c r="I7">
-        <v>0.1286173633440514</v>
+        <v>0.6203995793901157</v>
       </c>
       <c r="J7">
-        <v>0.07487367937528708</v>
+        <v>0.4471348319928762</v>
       </c>
       <c r="K7">
-        <v>6.55</v>
+        <v>0.16</v>
       </c>
       <c r="L7">
-        <v>0.07020364415862808</v>
+        <v>0.01682439537329127</v>
       </c>
       <c r="M7">
-        <v>4.97</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N7">
-        <v>0.01680757524518093</v>
+        <v>0.3960869565217391</v>
       </c>
       <c r="O7">
-        <v>0.7587786259541984</v>
+        <v>56.93749999999999</v>
       </c>
       <c r="P7">
-        <v>4.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>0.01680757524518093</v>
+        <v>0.1565217391304348</v>
       </c>
       <c r="R7">
-        <v>0.7587786259541984</v>
+        <v>22.5</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.6048298572996708</v>
       </c>
       <c r="U7">
-        <v>15.4</v>
+        <v>5.09</v>
       </c>
       <c r="V7">
-        <v>0.05207981061887048</v>
+        <v>0.221304347826087</v>
       </c>
       <c r="W7">
-        <v>0.3133971291866029</v>
+        <v>0.002935779816513761</v>
       </c>
       <c r="X7">
-        <v>0.05164057461063938</v>
+        <v>0.08670286556839511</v>
       </c>
       <c r="Y7">
-        <v>0.2617565545759635</v>
+        <v>-0.08376708575188135</v>
       </c>
       <c r="Z7">
-        <v>4.573529411764706</v>
+        <v>0.2250887573964497</v>
       </c>
       <c r="AA7">
-        <v>0.342436974789916</v>
+        <v>0.1006450237219468</v>
       </c>
       <c r="AB7">
-        <v>0.04919288587961176</v>
+        <v>0.0795436077537208</v>
       </c>
       <c r="AC7">
-        <v>0.2932440889103042</v>
+        <v>0.021101415968226</v>
       </c>
       <c r="AD7">
-        <v>31.4</v>
+        <v>5.39</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>31.4</v>
+        <v>5.39</v>
       </c>
       <c r="AG7">
-        <v>16</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="AH7">
-        <v>0.09599510852950169</v>
+        <v>0.1898555829517436</v>
       </c>
       <c r="AI7">
-        <v>0.4610866372980911</v>
+        <v>0.1046805204894154</v>
       </c>
       <c r="AJ7">
-        <v>0.05133140840551812</v>
+        <v>0.01287553648068669</v>
       </c>
       <c r="AK7">
-        <v>0.3036053130929791</v>
+        <v>0.006465517241379307</v>
       </c>
       <c r="AL7">
-        <v>1.17</v>
+        <v>0.312</v>
       </c>
       <c r="AM7">
-        <v>1.125</v>
+        <v>0.312</v>
       </c>
       <c r="AN7">
-        <v>2.47244094488189</v>
+        <v>0.9120135363790185</v>
       </c>
       <c r="AO7">
-        <v>10.25641025641026</v>
+        <v>18.91025641025641</v>
       </c>
       <c r="AP7">
-        <v>1.259842519685039</v>
+        <v>0.05076142131979693</v>
       </c>
       <c r="AQ7">
-        <v>10.66666666666667</v>
+        <v>18.91025641025641</v>
       </c>
     </row>
     <row r="8">
@@ -1281,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital Point Ltd. (TASE:CPTP)</t>
+          <t>E.N. Shoham Business Ltd (TASE:SHOM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1290,121 +1365,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0698</v>
+        <v>0.403</v>
       </c>
       <c r="E8">
-        <v>0.232</v>
+        <v>0.528</v>
       </c>
       <c r="G8">
-        <v>0.7857142857142856</v>
+        <v>0.6639004149377593</v>
       </c>
       <c r="H8">
-        <v>0.7857142857142856</v>
+        <v>0.6639004149377593</v>
       </c>
       <c r="I8">
-        <v>0.7678571428571428</v>
+        <v>0.8506224066390041</v>
       </c>
       <c r="J8">
-        <v>0.6070303712035995</v>
+        <v>0.6475280645887612</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="L8">
-        <v>0.5952380952380952</v>
+        <v>0.4078838174273859</v>
       </c>
       <c r="M8">
-        <v>3.9122</v>
+        <v>1.486</v>
       </c>
       <c r="N8">
-        <v>0.102413612565445</v>
+        <v>0.02321875</v>
       </c>
       <c r="O8">
-        <v>0.39122</v>
+        <v>0.1511698880976602</v>
       </c>
       <c r="P8">
-        <v>3.9122</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>0.102413612565445</v>
+        <v>0.021875</v>
       </c>
       <c r="R8">
-        <v>0.39122</v>
+        <v>0.1424211597151577</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.08600000000000008</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.05787348586810234</v>
       </c>
       <c r="U8">
-        <v>17.9</v>
+        <v>14.1</v>
       </c>
       <c r="V8">
-        <v>0.4685863874345549</v>
+        <v>0.2203125</v>
       </c>
       <c r="W8">
-        <v>0.2386634844868735</v>
+        <v>0.2769014084507042</v>
       </c>
       <c r="X8">
-        <v>0.05272561695192858</v>
+        <v>0.1682871329972423</v>
       </c>
       <c r="Y8">
-        <v>0.185937867534945</v>
+        <v>0.1086142754534619</v>
       </c>
       <c r="Z8">
-        <v>0.5174006775485064</v>
+        <v>0.1428825517282267</v>
       </c>
       <c r="AA8">
-        <v>0.3140779253532637</v>
+        <v>0.09252046218408222</v>
       </c>
       <c r="AB8">
-        <v>0.04884227944545544</v>
+        <v>0.07562980347321936</v>
       </c>
       <c r="AC8">
-        <v>0.2652356459078083</v>
+        <v>0.01689065871086286</v>
       </c>
       <c r="AD8">
-        <v>5.65</v>
+        <v>182.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>5.65</v>
+        <v>182.1</v>
       </c>
       <c r="AG8">
-        <v>-12.25</v>
+        <v>168</v>
       </c>
       <c r="AH8">
-        <v>0.12884834663626</v>
+        <v>0.7399431125558716</v>
       </c>
       <c r="AI8">
-        <v>0.09393183707398171</v>
+        <v>0.816591928251121</v>
       </c>
       <c r="AJ8">
-        <v>-0.4720616570327552</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="AK8">
-        <v>-0.2899408284023668</v>
+        <v>0.8042125418860698</v>
       </c>
       <c r="AL8">
-        <v>0.229</v>
+        <v>6.78</v>
       </c>
       <c r="AM8">
-        <v>0.229</v>
+        <v>6.78</v>
       </c>
       <c r="AN8">
-        <v>0.437984496124031</v>
+        <v>8.839805825242717</v>
       </c>
       <c r="AO8">
-        <v>56.33187772925764</v>
+        <v>3.023598820058997</v>
       </c>
       <c r="AP8">
-        <v>-0.949612403100775</v>
+        <v>8.155339805825243</v>
       </c>
       <c r="AQ8">
-        <v>56.33187772925764</v>
+        <v>3.023598820058997</v>
       </c>
     </row>
     <row r="9">
@@ -1415,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Generation Capital Ltd (TASE:GNRS)</t>
+          <t>Meitav Investment House Ltd (TASE:MTAV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1423,41 +1498,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0638</v>
+      </c>
+      <c r="E9">
+        <v>0.022</v>
+      </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.3629652414641649</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.3629652414641649</v>
       </c>
       <c r="I9">
-        <v>0.9060014461315978</v>
+        <v>0.2537680713626576</v>
       </c>
       <c r="J9">
-        <v>0.7145926899066124</v>
+        <v>0.1526354082365801</v>
       </c>
       <c r="K9">
-        <v>95.2</v>
+        <v>27.2</v>
       </c>
       <c r="L9">
-        <v>0.6883586406362978</v>
+        <v>0.08366656413411257</v>
       </c>
       <c r="M9">
-        <v>15.5</v>
+        <v>7.1797</v>
       </c>
       <c r="N9">
-        <v>0.03466785953925296</v>
+        <v>0.03330102040816326</v>
       </c>
       <c r="O9">
-        <v>0.1628151260504202</v>
+        <v>0.2639595588235294</v>
       </c>
       <c r="P9">
-        <v>15.5</v>
+        <v>7.1797</v>
       </c>
       <c r="Q9">
-        <v>0.03466785953925296</v>
+        <v>0.03330102040816326</v>
       </c>
       <c r="R9">
-        <v>0.1628151260504202</v>
+        <v>0.2639595588235294</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1466,67 +1547,70 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>139.2</v>
+        <v>82</v>
       </c>
       <c r="V9">
-        <v>0.3113397450234847</v>
+        <v>0.3803339517625232</v>
       </c>
       <c r="W9">
-        <v>0.2751445086705203</v>
+        <v>0.1851599727705922</v>
       </c>
       <c r="X9">
-        <v>0.06010622071538786</v>
+        <v>0.1908310006530669</v>
       </c>
       <c r="Y9">
-        <v>0.2150382879551324</v>
+        <v>-0.005671027882474616</v>
       </c>
       <c r="Z9">
-        <v>0.4170687575392039</v>
+        <v>0.5216623876765084</v>
       </c>
       <c r="AA9">
-        <v>0.2980342853259484</v>
+        <v>0.07962415150467296</v>
       </c>
       <c r="AB9">
-        <v>0.04879353620452694</v>
+        <v>0.07542156320871077</v>
       </c>
       <c r="AC9">
-        <v>0.2492407491214215</v>
+        <v>0.004202588295962192</v>
       </c>
       <c r="AD9">
-        <v>193</v>
+        <v>769</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>193</v>
+        <v>769</v>
       </c>
       <c r="AG9">
-        <v>53.80000000000001</v>
+        <v>687</v>
       </c>
       <c r="AH9">
-        <v>0.3015153882205905</v>
+        <v>0.7810278285598212</v>
       </c>
       <c r="AI9">
-        <v>0.2795885846733305</v>
+        <v>0.7879905728045906</v>
       </c>
       <c r="AJ9">
-        <v>0.1074066679976043</v>
+        <v>0.7611345003323732</v>
       </c>
       <c r="AK9">
-        <v>0.09762293594628926</v>
+        <v>0.7685423425439087</v>
       </c>
       <c r="AL9">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.816</v>
-      </c>
-      <c r="AO9">
-        <v>32.46113989637306</v>
+        <v>-39</v>
+      </c>
+      <c r="AN9">
+        <v>8.478500551267915</v>
+      </c>
+      <c r="AP9">
+        <v>7.574421168687982</v>
       </c>
       <c r="AQ9">
-        <v>32.83542976939204</v>
+        <v>-2.115384615384615</v>
       </c>
     </row>
     <row r="10">
@@ -1537,7 +1621,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meitav DASH Investments Ltd (TASE:MTDS)</t>
+          <t>Unicorn Technologies - Limited Partnership (TASE:UNCT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1545,119 +1629,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.08160000000000001</v>
-      </c>
       <c r="G10">
-        <v>0.2811244979919679</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.2811244979919679</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.3138267355134825</v>
+        <v>0.3712418300653594</v>
       </c>
       <c r="J10">
-        <v>0.3138267355134825</v>
+        <v>0.3712418300653594</v>
       </c>
       <c r="K10">
-        <v>-108.5</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="L10">
-        <v>-0.3112449799196787</v>
+        <v>0.3699346405228758</v>
       </c>
       <c r="M10">
-        <v>25.68</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.07171181234292097</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0.2366820276497696</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>23.2</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.06478637252164199</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0.2138248847926267</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>2.48</v>
-      </c>
-      <c r="T10">
-        <v>0.09657320872274146</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>86.09999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="V10">
-        <v>0.2404356325048869</v>
+        <v>2.819620253164557</v>
       </c>
       <c r="W10">
-        <v>-0.4085090361445783</v>
+        <v>0.02788177339901477</v>
       </c>
       <c r="X10">
-        <v>0.08972695793106038</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y10">
-        <v>-0.4982359940756387</v>
+        <v>-0.05149847463040248</v>
       </c>
       <c r="Z10">
-        <v>0.5926555593335601</v>
+        <v>0.2095890410958904</v>
       </c>
       <c r="AA10">
-        <v>0.1859911594695682</v>
+        <v>0.07780821917808217</v>
       </c>
       <c r="AB10">
-        <v>0.05087862644722159</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC10">
-        <v>0.1351125330223466</v>
+        <v>-0.001572028851335089</v>
       </c>
       <c r="AD10">
-        <v>562.4</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>562.4</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>476.3</v>
+        <v>-8.91</v>
       </c>
       <c r="AH10">
-        <v>0.6109722976643128</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.7280258899676375</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.5708293384467881</v>
+        <v>1.549565217391304</v>
       </c>
       <c r="AK10">
-        <v>0.6939102564102564</v>
+        <v>-0.891891891891892</v>
       </c>
       <c r="AL10">
-        <v>91.7</v>
+        <v>0.002</v>
       </c>
       <c r="AM10">
-        <v>81.78</v>
-      </c>
-      <c r="AN10">
-        <v>4.726050420168067</v>
+        <v>0.002</v>
       </c>
       <c r="AO10">
-        <v>1.193020719738277</v>
-      </c>
-      <c r="AP10">
-        <v>4.002521008403361</v>
+        <v>283.9999999999999</v>
       </c>
       <c r="AQ10">
-        <v>1.337735387625336</v>
+        <v>283.9999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1668,7 +1740,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vision Sigma Ltd. (TASE:VISN)</t>
+          <t>Analyst I.M.S. Investment Management Services Ltd (TASE:ANLT)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1676,41 +1748,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.09630000000000001</v>
+      </c>
+      <c r="E11">
+        <v>-0.301</v>
+      </c>
       <c r="G11">
-        <v>-0.4928229665071771</v>
+        <v>0.1462264150943396</v>
       </c>
       <c r="H11">
-        <v>-0.4928229665071771</v>
+        <v>0.1462264150943396</v>
       </c>
       <c r="I11">
-        <v>0.7527910685805422</v>
+        <v>0.1025943396226415</v>
       </c>
       <c r="J11">
-        <v>0.6466499484607455</v>
+        <v>0.05129716981132075</v>
       </c>
       <c r="K11">
-        <v>5.34</v>
+        <v>0.273</v>
       </c>
       <c r="L11">
-        <v>0.8516746411483254</v>
+        <v>0.00643867924528302</v>
       </c>
       <c r="M11">
-        <v>0.48208</v>
+        <v>1.47</v>
       </c>
       <c r="N11">
-        <v>0.02152142857142857</v>
+        <v>0.01501532175689479</v>
       </c>
       <c r="O11">
-        <v>0.09027715355805244</v>
+        <v>5.384615384615384</v>
       </c>
       <c r="P11">
-        <v>0.48208</v>
+        <v>1.47</v>
       </c>
       <c r="Q11">
-        <v>0.02152142857142857</v>
+        <v>0.01501532175689479</v>
       </c>
       <c r="R11">
-        <v>0.09027715355805244</v>
+        <v>5.384615384615384</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1719,73 +1797,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>3.27</v>
+        <v>13</v>
       </c>
       <c r="V11">
-        <v>0.1459821428571429</v>
+        <v>0.1327885597548519</v>
       </c>
       <c r="W11">
-        <v>0.2427272727272727</v>
+        <v>0.005438247011952191</v>
       </c>
       <c r="X11">
-        <v>0.07488821552244272</v>
+        <v>0.08116441106918254</v>
       </c>
       <c r="Y11">
-        <v>0.16783905720483</v>
+        <v>-0.07572616405723034</v>
       </c>
       <c r="Z11">
-        <v>0.2055063913470993</v>
+        <v>1.037181996086106</v>
       </c>
       <c r="AA11">
-        <v>0.1328906973729556</v>
+        <v>0.05320450097847357</v>
       </c>
       <c r="AB11">
-        <v>0.0505153666601854</v>
+        <v>0.07910647047583855</v>
       </c>
       <c r="AC11">
-        <v>0.08237533071277019</v>
+        <v>-0.02590196949736497</v>
       </c>
       <c r="AD11">
-        <v>22.4</v>
+        <v>5.59</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>22.4</v>
+        <v>5.59</v>
       </c>
       <c r="AG11">
-        <v>19.13</v>
+        <v>-7.41</v>
       </c>
       <c r="AH11">
-        <v>0.5</v>
+        <v>0.05401488066479852</v>
       </c>
       <c r="AI11">
-        <v>0.4374999999999999</v>
+        <v>0.1085647698582249</v>
       </c>
       <c r="AJ11">
-        <v>0.4606308692511437</v>
+        <v>-0.08188750138136811</v>
       </c>
       <c r="AK11">
-        <v>0.3991237220947215</v>
+        <v>-0.1925175370226033</v>
       </c>
       <c r="AL11">
-        <v>0.413</v>
+        <v>0.256</v>
       </c>
       <c r="AM11">
-        <v>0.413</v>
+        <v>0.169</v>
       </c>
       <c r="AN11">
-        <v>4.590163934426229</v>
+        <v>1.025688073394495</v>
       </c>
       <c r="AO11">
-        <v>11.42857142857143</v>
+        <v>16.9921875</v>
       </c>
       <c r="AP11">
-        <v>3.920081967213115</v>
+        <v>-1.359633027522936</v>
       </c>
       <c r="AQ11">
-        <v>11.42857142857143</v>
+        <v>25.7396449704142</v>
       </c>
     </row>
     <row r="12">
@@ -1796,7 +1874,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E.N. Shoham Business Ltd (TASE:SHOM)</t>
+          <t>Almeda Ventures Limited Partnership (TASE:AMDA)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1804,119 +1882,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>1.044</v>
-      </c>
-      <c r="G12">
-        <v>0.6729559748427673</v>
-      </c>
-      <c r="H12">
-        <v>0.6729559748427673</v>
-      </c>
-      <c r="I12">
-        <v>0.8113207547169812</v>
-      </c>
-      <c r="J12">
-        <v>0.6066910586603534</v>
-      </c>
       <c r="K12">
-        <v>5.89</v>
-      </c>
-      <c r="L12">
-        <v>0.370440251572327</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3.1</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.0292177191328935</v>
-      </c>
-      <c r="O12">
-        <v>0.5263157894736843</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.0292177191328935</v>
-      </c>
-      <c r="R12">
-        <v>0.5263157894736843</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>2.03</v>
+        <v>6.44</v>
       </c>
       <c r="V12">
-        <v>0.01913289349670122</v>
+        <v>1.387931034482759</v>
       </c>
       <c r="W12">
-        <v>0.2404081632653061</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>0.08202184675835902</v>
+        <v>0.08048466046932132</v>
       </c>
       <c r="Y12">
-        <v>0.1583863165069471</v>
+        <v>-0.08048466046932132</v>
       </c>
       <c r="Z12">
-        <v>0.1786516853932584</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0.1083863801426924</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.05071274905653447</v>
+        <v>0.07950951041365367</v>
       </c>
       <c r="AC12">
-        <v>0.05767363108615789</v>
+        <v>-0.07950951041365367</v>
       </c>
       <c r="AD12">
-        <v>135.2</v>
+        <v>0.164</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>135.2</v>
+        <v>0.164</v>
       </c>
       <c r="AG12">
-        <v>133.17</v>
+        <v>-6.276000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.5602983837546622</v>
+        <v>0.03413821815154039</v>
       </c>
       <c r="AI12">
-        <v>0.79203280609256</v>
+        <v>0.005928282244071718</v>
       </c>
       <c r="AJ12">
-        <v>0.55656789401095</v>
+        <v>3.836185819070903</v>
       </c>
       <c r="AK12">
-        <v>0.7895298511887117</v>
+        <v>-0.2957029777610253</v>
       </c>
       <c r="AL12">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.47</v>
-      </c>
-      <c r="AN12">
-        <v>10.4</v>
-      </c>
-      <c r="AO12">
-        <v>2.885906040268456</v>
-      </c>
-      <c r="AP12">
-        <v>10.24384615384615</v>
-      </c>
-      <c r="AQ12">
-        <v>2.885906040268456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1927,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analyst I.M.S. Investment Management Services Ltd (TASE:ANLT)</t>
+          <t>Vision Sigma Ltd. (TASE:VISN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1936,46 +1975,46 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.114</v>
+        <v>-0.245</v>
       </c>
       <c r="E13">
-        <v>0.402</v>
+        <v>0.0646</v>
       </c>
       <c r="G13">
-        <v>0.1679886685552408</v>
+        <v>1.326797385620915</v>
       </c>
       <c r="H13">
-        <v>0.1679886685552408</v>
+        <v>1.326797385620915</v>
       </c>
       <c r="I13">
-        <v>0.1498583569405099</v>
+        <v>-0.2464052287581699</v>
       </c>
       <c r="J13">
-        <v>0.08938734389338866</v>
+        <v>-0.1764720374476472</v>
       </c>
       <c r="K13">
-        <v>8.460000000000001</v>
+        <v>6.46</v>
       </c>
       <c r="L13">
-        <v>0.2396600566572238</v>
+        <v>4.222222222222222</v>
       </c>
       <c r="M13">
-        <v>5.62</v>
+        <v>0.453</v>
       </c>
       <c r="N13">
-        <v>0.04435674822415154</v>
+        <v>0.02031390134529148</v>
       </c>
       <c r="O13">
-        <v>0.6643026004728132</v>
+        <v>0.07012383900928792</v>
       </c>
       <c r="P13">
-        <v>5.62</v>
+        <v>0.453</v>
       </c>
       <c r="Q13">
-        <v>0.04435674822415154</v>
+        <v>0.02031390134529148</v>
       </c>
       <c r="R13">
-        <v>0.6643026004728132</v>
+        <v>0.07012383900928792</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1984,73 +2023,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>15.9</v>
+        <v>6.1</v>
       </c>
       <c r="V13">
-        <v>0.1254932912391476</v>
+        <v>0.2735426008968609</v>
       </c>
       <c r="W13">
-        <v>0.1940366972477064</v>
+        <v>0.2243055555555555</v>
       </c>
       <c r="X13">
-        <v>0.05022942570625705</v>
+        <v>0.1544846424989289</v>
       </c>
       <c r="Y13">
-        <v>0.1438072715414494</v>
+        <v>0.06982091305662663</v>
       </c>
       <c r="Z13">
-        <v>0.9537962712780328</v>
+        <v>0.03192155226371792</v>
       </c>
       <c r="AA13">
-        <v>0.08525731530496135</v>
+        <v>-0.005633261366469856</v>
       </c>
       <c r="AB13">
-        <v>0.04904026113515258</v>
+        <v>0.08205420446049808</v>
       </c>
       <c r="AC13">
-        <v>0.03621705416980877</v>
+        <v>-0.08768746582696793</v>
       </c>
       <c r="AD13">
-        <v>6.58</v>
+        <v>53.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>6.58</v>
+        <v>53.6</v>
       </c>
       <c r="AG13">
-        <v>-9.32</v>
+        <v>47.5</v>
       </c>
       <c r="AH13">
-        <v>0.04936974789915966</v>
+        <v>0.7061923583662714</v>
       </c>
       <c r="AI13">
-        <v>0.1158858753082071</v>
+        <v>0.6203703703703703</v>
       </c>
       <c r="AJ13">
-        <v>-0.07940023854148918</v>
+        <v>0.6805157593123209</v>
       </c>
       <c r="AK13">
-        <v>-0.2279843444227006</v>
+        <v>0.5915317559153176</v>
       </c>
       <c r="AL13">
-        <v>0.271</v>
+        <v>0.839</v>
       </c>
       <c r="AM13">
-        <v>0.264</v>
+        <v>0.839</v>
       </c>
       <c r="AN13">
-        <v>1.056179775280899</v>
+        <v>-261.4634146341464</v>
       </c>
       <c r="AO13">
-        <v>19.52029520295203</v>
+        <v>-0.4493444576877235</v>
       </c>
       <c r="AP13">
-        <v>-1.495987158908507</v>
+        <v>-231.7073170731707</v>
       </c>
       <c r="AQ13">
-        <v>20.03787878787879</v>
+        <v>-0.4493444576877235</v>
       </c>
     </row>
     <row r="14">
@@ -2070,22 +2109,22 @@
         </is>
       </c>
       <c r="G14">
-        <v>0.1172602739726027</v>
+        <v>0.04506437768240344</v>
       </c>
       <c r="H14">
-        <v>0.1172602739726027</v>
+        <v>0.04506437768240344</v>
       </c>
       <c r="I14">
-        <v>0.1668493150684932</v>
+        <v>-0.07296137339055793</v>
       </c>
       <c r="J14">
-        <v>0.1314122923990787</v>
+        <v>-0.05366191333241035</v>
       </c>
       <c r="K14">
-        <v>8.93</v>
+        <v>11.4</v>
       </c>
       <c r="L14">
-        <v>0.2446575342465753</v>
+        <v>0.2446351931330472</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2109,73 +2148,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>9.09</v>
+        <v>5.97</v>
       </c>
       <c r="V14">
-        <v>0.1095180722891566</v>
+        <v>0.09328125</v>
       </c>
       <c r="W14">
-        <v>0.1675422138836773</v>
+        <v>0.1610169491525424</v>
       </c>
       <c r="X14">
-        <v>0.08701556583456083</v>
+        <v>0.1714606352064178</v>
       </c>
       <c r="Y14">
-        <v>0.08052664804911647</v>
+        <v>-0.01044368605387544</v>
       </c>
       <c r="Z14">
-        <v>0.251031636863824</v>
+        <v>0.2540755683986697</v>
       </c>
       <c r="AA14">
-        <v>0.03298864286496817</v>
+        <v>-0.01363418113129231</v>
       </c>
       <c r="AB14">
-        <v>0.05082479912201462</v>
+        <v>0.08002268416541258</v>
       </c>
       <c r="AC14">
-        <v>-0.01783615625704645</v>
+        <v>-0.09365686529670489</v>
       </c>
       <c r="AD14">
-        <v>121.7</v>
+        <v>188.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>121.7</v>
+        <v>188.6</v>
       </c>
       <c r="AG14">
-        <v>112.61</v>
+        <v>182.63</v>
       </c>
       <c r="AH14">
-        <v>0.5945285784074256</v>
+        <v>0.7466349960411718</v>
       </c>
       <c r="AI14">
-        <v>0.6322077922077922</v>
+        <v>0.6735714285714286</v>
       </c>
       <c r="AJ14">
-        <v>0.5756863146055927</v>
+        <v>0.7405019665085351</v>
       </c>
       <c r="AK14">
-        <v>0.6139796085273431</v>
+        <v>0.6664598766558406</v>
       </c>
       <c r="AL14">
-        <v>2.78</v>
+        <v>4.41</v>
       </c>
       <c r="AM14">
-        <v>2.617</v>
+        <v>4.365</v>
       </c>
       <c r="AN14">
-        <v>19.75649350649351</v>
+        <v>-56.80722891566265</v>
       </c>
       <c r="AO14">
-        <v>2.190647482014389</v>
+        <v>-0.7709750566893424</v>
       </c>
       <c r="AP14">
-        <v>18.28084415584415</v>
+        <v>-55.00903614457832</v>
       </c>
       <c r="AQ14">
-        <v>2.327092090179595</v>
+        <v>-0.7789232531500572</v>
       </c>
     </row>
     <row r="15">
@@ -2186,7 +2225,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eldav Investments Ltd. (TASE:ELDAV)</t>
+          <t>TechnoPlus Ventures Ltd. (TASE:TNPV)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2195,43 +2234,43 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0132</v>
+        <v>-0.0208</v>
       </c>
       <c r="G15">
-        <v>-0.003036211699164346</v>
+        <v>0.0748502994011976</v>
       </c>
       <c r="H15">
-        <v>-0.007604456824512535</v>
+        <v>0.0748502994011976</v>
       </c>
       <c r="I15">
-        <v>0.01303621169916435</v>
+        <v>-0.3323353293413174</v>
       </c>
       <c r="J15">
-        <v>0.01194299956018179</v>
+        <v>-0.3323353293413174</v>
       </c>
       <c r="K15">
-        <v>10.4</v>
+        <v>-0.304</v>
       </c>
       <c r="L15">
-        <v>0.2896935933147632</v>
+        <v>-0.9101796407185628</v>
       </c>
       <c r="M15">
-        <v>3.07</v>
+        <v>1.18146</v>
       </c>
       <c r="N15">
-        <v>0.1040677966101695</v>
+        <v>0.2152021857923497</v>
       </c>
       <c r="O15">
-        <v>0.2951923076923076</v>
+        <v>-3.886381578947368</v>
       </c>
       <c r="P15">
-        <v>3.07</v>
+        <v>1.18146</v>
       </c>
       <c r="Q15">
-        <v>0.1040677966101695</v>
+        <v>0.2152021857923497</v>
       </c>
       <c r="R15">
-        <v>0.2951923076923076</v>
+        <v>-3.886381578947368</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2240,70 +2279,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2.38</v>
+        <v>5.13</v>
       </c>
       <c r="V15">
-        <v>0.08067796610169491</v>
+        <v>0.9344262295081966</v>
       </c>
       <c r="W15">
-        <v>0.4333333333333333</v>
+        <v>-0.06770601336302895</v>
       </c>
       <c r="X15">
-        <v>0.06369087836656859</v>
+        <v>0.08165688125219697</v>
       </c>
       <c r="Y15">
-        <v>0.3696424549667647</v>
+        <v>-0.1493628946152259</v>
       </c>
       <c r="Z15">
-        <v>0.889737044288582</v>
+        <v>0.1312893081761006</v>
       </c>
       <c r="AA15">
-        <v>0.01062612912861598</v>
+        <v>-0.04363207547169811</v>
       </c>
       <c r="AB15">
-        <v>0.05006641924015043</v>
+        <v>0.07943868212352953</v>
       </c>
       <c r="AC15">
-        <v>-0.03944029011153444</v>
+        <v>-0.1230707575952276</v>
       </c>
       <c r="AD15">
-        <v>16.8</v>
+        <v>0.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>16.8</v>
+        <v>0.4</v>
       </c>
       <c r="AG15">
-        <v>14.42</v>
+        <v>-4.73</v>
       </c>
       <c r="AH15">
-        <v>0.3628509719222462</v>
+        <v>0.06791171477079797</v>
       </c>
       <c r="AI15">
-        <v>0.336</v>
+        <v>0.05398110661268556</v>
       </c>
       <c r="AJ15">
-        <v>0.3283242258652095</v>
+        <v>-6.22368421052631</v>
       </c>
       <c r="AK15">
-        <v>0.3028139437211256</v>
+        <v>-2.074561403508771</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>0.321</v>
       </c>
       <c r="AM15">
-        <v>-1.83</v>
+        <v>0.32</v>
       </c>
       <c r="AN15">
-        <v>9.940828402366865</v>
+        <v>-3.636363636363637</v>
+      </c>
+      <c r="AO15">
+        <v>-0.3457943925233645</v>
       </c>
       <c r="AP15">
-        <v>8.532544378698226</v>
+        <v>42.99999999999999</v>
       </c>
       <c r="AQ15">
-        <v>-0.2557377049180328</v>
+        <v>-0.346875</v>
       </c>
     </row>
     <row r="16">
@@ -2314,7 +2356,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TechnoPlus Ventures Ltd. (TASE:TNPV)</t>
+          <t>Eldav Investments Ltd. (TASE:ELDAV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2323,118 +2365,121 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.319</v>
+        <v>-0.7509999999999999</v>
+      </c>
+      <c r="E16">
+        <v>1.09</v>
       </c>
       <c r="G16">
-        <v>-0.863013698630137</v>
+        <v>-57.61904761904763</v>
       </c>
       <c r="H16">
-        <v>-0.863013698630137</v>
+        <v>-57.85714285714285</v>
       </c>
       <c r="I16">
-        <v>-0.678082191780822</v>
+        <v>-64.76190476190476</v>
       </c>
       <c r="J16">
-        <v>-0.678082191780822</v>
+        <v>-48.83809523809524</v>
       </c>
       <c r="K16">
-        <v>-0.546</v>
+        <v>12.9</v>
       </c>
       <c r="L16">
-        <v>-1.86986301369863</v>
+        <v>307.1428571428571</v>
       </c>
       <c r="M16">
-        <v>6.01</v>
+        <v>3.957</v>
       </c>
       <c r="N16">
-        <v>0.635978835978836</v>
+        <v>0.1527799227799228</v>
       </c>
       <c r="O16">
-        <v>-11.00732600732601</v>
+        <v>0.3067441860465116</v>
       </c>
       <c r="P16">
-        <v>6.01</v>
+        <v>3.86</v>
       </c>
       <c r="Q16">
-        <v>0.635978835978836</v>
+        <v>0.149034749034749</v>
       </c>
       <c r="R16">
-        <v>-11.00732600732601</v>
+        <v>0.2992248062015504</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>0.09699999999999998</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.02451352034369471</v>
       </c>
       <c r="U16">
+        <v>13</v>
+      </c>
+      <c r="V16">
+        <v>0.5019305019305019</v>
+      </c>
+      <c r="W16">
+        <v>0.3553719008264463</v>
+      </c>
+      <c r="X16">
+        <v>0.08221538157417521</v>
+      </c>
+      <c r="Y16">
+        <v>0.2731565192522711</v>
+      </c>
+      <c r="Z16">
+        <v>0.001146914254505735</v>
+      </c>
+      <c r="AA16">
+        <v>-0.05601310759148007</v>
+      </c>
+      <c r="AB16">
+        <v>0.07895861577398849</v>
+      </c>
+      <c r="AC16">
+        <v>-0.1349717233654686</v>
+      </c>
+      <c r="AD16">
         <v>2.35</v>
       </c>
-      <c r="V16">
-        <v>0.2486772486772487</v>
-      </c>
-      <c r="W16">
-        <v>-0.05102803738317758</v>
-      </c>
-      <c r="X16">
-        <v>0.04999059604650137</v>
-      </c>
-      <c r="Y16">
-        <v>-0.101018633429679</v>
-      </c>
-      <c r="Z16">
-        <v>0.02796934865900384</v>
-      </c>
-      <c r="AA16">
-        <v>-0.01896551724137932</v>
-      </c>
-      <c r="AB16">
-        <v>0.04901285872029641</v>
-      </c>
-      <c r="AC16">
-        <v>-0.06797837596167573</v>
-      </c>
-      <c r="AD16">
-        <v>0.404</v>
-      </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0.404</v>
+        <v>2.35</v>
       </c>
       <c r="AG16">
-        <v>-1.946</v>
+        <v>-10.65</v>
       </c>
       <c r="AH16">
-        <v>0.04099857925715446</v>
+        <v>0.0831858407079646</v>
       </c>
       <c r="AI16">
-        <v>0.08255006129955048</v>
+        <v>0.0473313192346425</v>
       </c>
       <c r="AJ16">
-        <v>-0.2593283582089553</v>
+        <v>-0.698360655737705</v>
       </c>
       <c r="AK16">
-        <v>-0.764937106918239</v>
+        <v>-0.2905866302864939</v>
       </c>
       <c r="AL16">
-        <v>0.307</v>
+        <v>0.112</v>
       </c>
       <c r="AM16">
-        <v>0.307</v>
+        <v>-0.638</v>
       </c>
       <c r="AN16">
-        <v>-2.04040404040404</v>
+        <v>-0.9670781893004115</v>
       </c>
       <c r="AO16">
-        <v>-0.6449511400651466</v>
+        <v>-24.28571428571429</v>
       </c>
       <c r="AP16">
-        <v>9.828282828282829</v>
+        <v>4.382716049382716</v>
       </c>
       <c r="AQ16">
-        <v>-0.6449511400651466</v>
+        <v>4.263322884012539</v>
       </c>
     </row>
     <row r="17">
@@ -2453,23 +2498,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D17">
+        <v>-0.542</v>
+      </c>
       <c r="G17">
-        <v>-1.246882793017456</v>
+        <v>32.30769230769231</v>
       </c>
       <c r="H17">
-        <v>-1.408977556109726</v>
+        <v>20.6508875739645</v>
       </c>
       <c r="I17">
-        <v>-0.3728179551122195</v>
+        <v>-79.28994082840237</v>
       </c>
       <c r="J17">
-        <v>-0.3728179551122195</v>
+        <v>-79.28994082840237</v>
       </c>
       <c r="K17">
-        <v>4.73</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L17">
-        <v>0.5897755610972569</v>
+        <v>-56.98224852071006</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2478,7 +2526,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2487,79 +2535,79 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>6.66</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="V17">
-        <v>0.1070739549839228</v>
+        <v>0.1550239234449761</v>
       </c>
       <c r="W17">
-        <v>0.04942528735632185</v>
+        <v>-0.09553571428571429</v>
       </c>
       <c r="X17">
-        <v>0.0522657502289808</v>
+        <v>0.08195175427296561</v>
       </c>
       <c r="Y17">
-        <v>-0.002840462872658954</v>
+        <v>-0.1774874685586799</v>
       </c>
       <c r="Z17">
-        <v>0.08512896720093409</v>
+        <v>0.001652973395931143</v>
       </c>
       <c r="AA17">
-        <v>-0.03173760747266745</v>
+        <v>-0.1310641627543036</v>
       </c>
       <c r="AB17">
-        <v>0.04925581875399464</v>
+        <v>0.0789948404388594</v>
       </c>
       <c r="AC17">
-        <v>-0.08099342622666209</v>
+        <v>-0.210059003193163</v>
       </c>
       <c r="AD17">
-        <v>8.1</v>
+        <v>5.16</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>8.1</v>
+        <v>5.16</v>
       </c>
       <c r="AG17">
-        <v>1.44</v>
+        <v>-4.56</v>
       </c>
       <c r="AH17">
-        <v>0.1152204836415363</v>
+        <v>0.07603890362511052</v>
       </c>
       <c r="AI17">
-        <v>0.07458563535911603</v>
+        <v>0.05193236714975846</v>
       </c>
       <c r="AJ17">
-        <v>0.02262727844123192</v>
+        <v>-0.07843137254901962</v>
       </c>
       <c r="AK17">
-        <v>0.01412595644496762</v>
+        <v>-0.05087014725568943</v>
       </c>
       <c r="AL17">
-        <v>0.751</v>
+        <v>1.52</v>
       </c>
       <c r="AM17">
-        <v>0.751</v>
+        <v>1.52</v>
       </c>
       <c r="AN17">
-        <v>-3.306122448979592</v>
+        <v>-0.4</v>
       </c>
       <c r="AO17">
-        <v>-3.981358189081226</v>
+        <v>-8.815789473684211</v>
       </c>
       <c r="AP17">
-        <v>-0.587755102040816</v>
+        <v>0.3534883720930233</v>
       </c>
       <c r="AQ17">
-        <v>-3.981358189081226</v>
+        <v>-8.815789473684211</v>
       </c>
     </row>
     <row r="18">
@@ -2570,7 +2618,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GO.D.M Investments Ltd. (TASE:GODM-M)</t>
+          <t>Feat Fund Investments - Limited Partnership (TASE:FEAT)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2578,8 +2626,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G18">
+        <v>-5.560344827586206</v>
+      </c>
+      <c r="H18">
+        <v>-5.560344827586206</v>
+      </c>
+      <c r="I18">
+        <v>-4.913793103448275</v>
+      </c>
+      <c r="J18">
+        <v>-4.913793103448275</v>
+      </c>
       <c r="K18">
-        <v>-0.6889999999999999</v>
+        <v>-1.14</v>
+      </c>
+      <c r="L18">
+        <v>-4.913793103448275</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2603,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>4.51</v>
       </c>
       <c r="V18">
-        <v>0.05235602094240837</v>
+        <v>2.478021978021978</v>
       </c>
       <c r="W18">
-        <v>-0.4687074829931973</v>
+        <v>-0.09743589743589744</v>
       </c>
       <c r="X18">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y18">
-        <v>-0.5175861358307355</v>
+        <v>-0.1768161454653147</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>0.09027237354085609</v>
       </c>
       <c r="AA18">
-        <v>-9.666666666666657</v>
+        <v>-0.4435797665369652</v>
       </c>
       <c r="AB18">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC18">
-        <v>-9.715545319504196</v>
+        <v>-0.5229600145663824</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -2639,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>-1</v>
+        <v>-4.51</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -2648,22 +2711,25 @@
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.05524861878453038</v>
+        <v>1.676579925650558</v>
       </c>
       <c r="AK18">
-        <v>7.04225352112676</v>
+        <v>-0.8525519848771265</v>
       </c>
       <c r="AL18">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>0.015</v>
-      </c>
-      <c r="AO18">
-        <v>-38.66666666666666</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AN18">
+        <v>-0</v>
+      </c>
+      <c r="AP18">
+        <v>3.956140350877193</v>
       </c>
       <c r="AQ18">
-        <v>-38.66666666666666</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="19">
@@ -2674,7 +2740,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Feat Fund Investments Limited Partnership (TASE:FEAT.L)</t>
+          <t>Gesher I Acquisition Corp. (NasdaqGM:GIAC)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="K19">
-        <v>-0.293</v>
+        <v>-3</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2707,45 +2773,345 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>9.130000000000001</v>
+        <v>0.183</v>
       </c>
       <c r="V19">
-        <v>1.755769230769231</v>
+        <v>0.001232323232323232</v>
+      </c>
+      <c r="W19">
+        <v>-300</v>
       </c>
       <c r="X19">
-        <v>0.04887865283753826</v>
+        <v>0.07964747647755173</v>
+      </c>
+      <c r="Y19">
+        <v>-300.0796474764775</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>-19.94623655913978</v>
       </c>
       <c r="AB19">
-        <v>0.04887865283753826</v>
+        <v>0.07933726833645786</v>
+      </c>
+      <c r="AC19">
+        <v>-20.02557382747624</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG19">
-        <v>-9.130000000000001</v>
+        <v>1.087</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.008479668825532482</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>-0.2326007326007326</v>
       </c>
       <c r="AJ19">
-        <v>2.323155216284987</v>
+        <v>0.007266674243082621</v>
       </c>
       <c r="AK19">
-        <v>-3.55252918287938</v>
+        <v>-0.1926280347332979</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
+        <v>-0.673</v>
+      </c>
+      <c r="AQ19">
+        <v>5.512630014858841</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Big Tech 50 R&amp;D-Limited Partnership (TASE:BIGT)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>-2.75</v>
+      </c>
+      <c r="M20">
+        <v>3.853</v>
+      </c>
+      <c r="N20">
+        <v>0.5512160228898426</v>
+      </c>
+      <c r="O20">
+        <v>-1.401090909090909</v>
+      </c>
+      <c r="P20">
+        <v>3.57</v>
+      </c>
+      <c r="Q20">
+        <v>0.5107296137339056</v>
+      </c>
+      <c r="R20">
+        <v>-1.298181818181818</v>
+      </c>
+      <c r="S20">
+        <v>0.2829999999999999</v>
+      </c>
+      <c r="T20">
+        <v>0.07344926031663637</v>
+      </c>
+      <c r="U20">
+        <v>6.1</v>
+      </c>
+      <c r="V20">
+        <v>0.8726752503576537</v>
+      </c>
+      <c r="W20">
+        <v>-1.131687242798354</v>
+      </c>
+      <c r="X20">
+        <v>0.07952776506839115</v>
+      </c>
+      <c r="Y20">
+        <v>-1.211215007866745</v>
+      </c>
+      <c r="AB20">
+        <v>0.07938429111459192</v>
+      </c>
+      <c r="AD20">
+        <v>0.033</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0.033</v>
+      </c>
+      <c r="AG20">
+        <v>-6.066999999999999</v>
+      </c>
+      <c r="AH20">
+        <v>0.004698846646732166</v>
+      </c>
+      <c r="AI20">
+        <v>0.001128861218485958</v>
+      </c>
+      <c r="AJ20">
+        <v>-6.573131094257848</v>
+      </c>
+      <c r="AK20">
+        <v>-0.2622660268879955</v>
+      </c>
+      <c r="AL20">
+        <v>0.015</v>
+      </c>
+      <c r="AM20">
+        <v>-0.046</v>
+      </c>
+      <c r="AO20">
+        <v>-226</v>
+      </c>
+      <c r="AQ20">
+        <v>73.69565217391305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mia Dynamics Motors Ltd (TASE:MIA)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>-13.8</v>
+      </c>
+      <c r="M21">
+        <v>0.918</v>
+      </c>
+      <c r="N21">
+        <v>0.04350710900473934</v>
+      </c>
+      <c r="O21">
+        <v>-0.06652173913043478</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0.918</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>2.55</v>
+      </c>
+      <c r="V21">
+        <v>0.1208530805687204</v>
+      </c>
+      <c r="W21">
+        <v>-16.08391608391608</v>
+      </c>
+      <c r="X21">
+        <v>0.07974158532798442</v>
+      </c>
+      <c r="Y21">
+        <v>-16.16365766924407</v>
+      </c>
+      <c r="AB21">
+        <v>0.07952300177083105</v>
+      </c>
+      <c r="AD21">
+        <v>0.244</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0.244</v>
+      </c>
+      <c r="AG21">
+        <v>-2.306</v>
+      </c>
+      <c r="AH21">
+        <v>0.01143178410794603</v>
+      </c>
+      <c r="AI21">
+        <v>0.07498463429625078</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.1226987336383952</v>
+      </c>
+      <c r="AK21">
+        <v>-3.275568181818183</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-0.011</v>
+      </c>
+      <c r="AN21">
+        <v>-0.3210526315789474</v>
+      </c>
+      <c r="AP21">
+        <v>3.034210526315789</v>
+      </c>
+      <c r="AQ21">
+        <v>74.45454545454545</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Spree Acquisition Corp. 1 Limited (NYSE:SHAP)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K22">
+        <v>-0.595</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0.094</v>
+      </c>
+      <c r="V22">
+        <v>0.0003517964071856288</v>
+      </c>
+      <c r="X22">
+        <v>0.07938024802941726</v>
+      </c>
+      <c r="AB22">
+        <v>0.07938024802941726</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>-0.094</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-0</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.0003519202114516334</v>
+      </c>
+      <c r="AK22">
+        <v>0.0105570530098832</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/israel/israel_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ22"/>
+  <dimension ref="A1:AQ23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05614999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="E2">
-        <v>0.0646</v>
+        <v>0.1843</v>
       </c>
       <c r="G2">
-        <v>0.2703330074771432</v>
+        <v>0.248063926902984</v>
       </c>
       <c r="H2">
-        <v>0.267589354194511</v>
+        <v>0.2453829882858403</v>
       </c>
       <c r="I2">
-        <v>0.393487502796899</v>
+        <v>0.3189714959571512</v>
       </c>
       <c r="J2">
-        <v>0.3292117772715555</v>
+        <v>0.271466634797972</v>
       </c>
       <c r="K2">
-        <v>200.17</v>
+        <v>178.792</v>
       </c>
       <c r="L2">
-        <v>0.2395102824180045</v>
+        <v>0.1474409034870344</v>
       </c>
       <c r="M2">
-        <v>62.06816</v>
+        <v>83.38800000000001</v>
       </c>
       <c r="N2">
-        <v>0.03458028859546493</v>
+        <v>0.04566278057355012</v>
       </c>
       <c r="O2">
-        <v>0.3100772343508018</v>
+        <v>0.4663967067877758</v>
       </c>
       <c r="P2">
-        <v>55.17416</v>
+        <v>80.69</v>
       </c>
       <c r="Q2">
-        <v>0.03073940609504708</v>
+        <v>0.04418537157000717</v>
       </c>
       <c r="R2">
-        <v>0.2756365089673777</v>
+        <v>0.4513065461541903</v>
       </c>
       <c r="S2">
-        <v>6.894</v>
+        <v>2.698</v>
       </c>
       <c r="T2">
-        <v>0.1110714414604847</v>
+        <v>0.03235477526742457</v>
       </c>
       <c r="U2">
-        <v>353.377</v>
+        <v>290.792</v>
       </c>
       <c r="V2">
-        <v>0.1968783776254945</v>
+        <v>0.1592359966487238</v>
       </c>
       <c r="W2">
-        <v>0.01666001020548348</v>
+        <v>0.03902439024390245</v>
       </c>
       <c r="X2">
-        <v>0.08180431776258129</v>
+        <v>0.06959435841286037</v>
       </c>
       <c r="Y2">
-        <v>-0.06514430755709781</v>
+        <v>-0.03056996816895792</v>
       </c>
       <c r="Z2">
-        <v>0.3983537670602793</v>
+        <v>0.3483185054735211</v>
       </c>
       <c r="AA2">
-        <v>-0.002816630683234928</v>
+        <v>0.01906462774863266</v>
       </c>
       <c r="AB2">
-        <v>0.07938024802941726</v>
+        <v>0.06755036550793454</v>
       </c>
       <c r="AC2">
-        <v>-0.0835984881203108</v>
+        <v>-0.04977739392822295</v>
       </c>
       <c r="AD2">
-        <v>1991.015</v>
+        <v>2060.541</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1991.015</v>
+        <v>2060.541</v>
       </c>
       <c r="AG2">
-        <v>1637.638</v>
+        <v>1769.749</v>
       </c>
       <c r="AH2">
-        <v>0.5259006079111654</v>
+        <v>0.5301502993147676</v>
       </c>
       <c r="AI2">
-        <v>0.52872444528832</v>
+        <v>0.5062199572233609</v>
       </c>
       <c r="AJ2">
-        <v>0.4770924604476338</v>
+        <v>0.4921548566583397</v>
       </c>
       <c r="AK2">
-        <v>0.4799195151213925</v>
+        <v>0.4682304253246461</v>
       </c>
       <c r="AL2">
-        <v>42.337</v>
+        <v>90.107</v>
       </c>
       <c r="AM2">
-        <v>0.2559999999999931</v>
+        <v>72.474</v>
       </c>
       <c r="AN2">
-        <v>8.841293101534225</v>
+        <v>6.409885430049493</v>
       </c>
       <c r="AO2">
-        <v>7.767579186054752</v>
+        <v>4.292629873372768</v>
       </c>
       <c r="AP2">
-        <v>7.272088634294722</v>
+        <v>5.505296099395577</v>
       </c>
       <c r="AQ2">
-        <v>1284.593750000035</v>
+        <v>5.337031211192979</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spring Ventures Ltd (TASE:SPRG)</t>
+          <t>More Provident Funds Ltd (TASE:MPP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,26 +721,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.7390000000000001</v>
-      </c>
       <c r="G3">
-        <v>0.8744186046511628</v>
+        <v>0.04289772727272727</v>
       </c>
       <c r="H3">
-        <v>0.8643410852713178</v>
+        <v>0.04289772727272727</v>
       </c>
       <c r="I3">
-        <v>0.9147286821705427</v>
+        <v>0.1183712121212121</v>
       </c>
       <c r="J3">
-        <v>0.6977738024249652</v>
+        <v>0.07757336716681378</v>
       </c>
       <c r="K3">
-        <v>17.8</v>
+        <v>6.78</v>
       </c>
       <c r="L3">
-        <v>0.689922480620155</v>
+        <v>0.06420454545454546</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,70 +761,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>13.6</v>
       </c>
       <c r="V3">
-        <v>0.07272727272727272</v>
-      </c>
-      <c r="W3">
-        <v>0.4472361809045227</v>
+        <v>0.09121395036887994</v>
       </c>
       <c r="X3">
-        <v>0.07948470944208655</v>
-      </c>
-      <c r="Y3">
-        <v>0.3677514714624361</v>
-      </c>
-      <c r="Z3">
-        <v>0.683805989928439</v>
-      </c>
-      <c r="AA3">
-        <v>0.4771419057133344</v>
+        <v>0.07550083483841696</v>
       </c>
       <c r="AB3">
-        <v>0.0793831149959246</v>
-      </c>
-      <c r="AC3">
-        <v>0.3977587907174098</v>
+        <v>0.06748823821720845</v>
       </c>
       <c r="AD3">
-        <v>0.114</v>
+        <v>53.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.114</v>
+        <v>53.3</v>
       </c>
       <c r="AG3">
-        <v>-2.366</v>
+        <v>39.7</v>
       </c>
       <c r="AH3">
-        <v>0.003331969369264044</v>
+        <v>0.2633399209486166</v>
       </c>
       <c r="AI3">
-        <v>0.002072199803686335</v>
+        <v>0.4801801801801802</v>
       </c>
       <c r="AJ3">
-        <v>-0.07455725720047898</v>
+        <v>0.2102754237288136</v>
       </c>
       <c r="AK3">
-        <v>-0.04503749952411772</v>
+        <v>0.4075975359342915</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM3">
-        <v>-0.002</v>
+        <v>2.19</v>
       </c>
       <c r="AN3">
-        <v>0.004810126582278481</v>
+        <v>4.068702290076335</v>
+      </c>
+      <c r="AO3">
+        <v>5.707762557077626</v>
       </c>
       <c r="AP3">
-        <v>-0.09983122362869198</v>
+        <v>3.030534351145038</v>
       </c>
       <c r="AQ3">
-        <v>-11800</v>
+        <v>5.707762557077626</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Keystone REIT Ltd. (TASE:KSTN)</t>
+          <t>Altshuler Shaham Finance Ltd (TASE:ALTF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,40 +832,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.3371559633027523</v>
+        <v>0.3599712023038157</v>
       </c>
       <c r="H4">
-        <v>0.3371559633027523</v>
+        <v>0.3599712023038157</v>
       </c>
       <c r="I4">
-        <v>0.9105504587155964</v>
+        <v>0.2242620590352772</v>
       </c>
       <c r="J4">
-        <v>0.6900584193853623</v>
+        <v>0.1497614428133885</v>
       </c>
       <c r="K4">
-        <v>50.7</v>
+        <v>39.4</v>
       </c>
       <c r="L4">
-        <v>0.5814220183486238</v>
+        <v>0.1418286537077034</v>
       </c>
       <c r="M4">
-        <v>11.2</v>
+        <v>32</v>
       </c>
       <c r="N4">
-        <v>0.08784313725490195</v>
+        <v>0.1077803974402156</v>
       </c>
       <c r="O4">
-        <v>0.2209072978303747</v>
+        <v>0.8121827411167513</v>
       </c>
       <c r="P4">
-        <v>11.2</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>0.08784313725490195</v>
+        <v>0.1077803974402156</v>
       </c>
       <c r="R4">
-        <v>0.2209072978303747</v>
+        <v>0.8121827411167513</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,73 +874,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>34.2</v>
+        <v>15.9</v>
       </c>
       <c r="V4">
-        <v>0.2682352941176471</v>
+        <v>0.05355338497810711</v>
       </c>
       <c r="W4">
-        <v>0.2848314606741573</v>
+        <v>0.2880116959064327</v>
       </c>
       <c r="X4">
-        <v>0.1593475256579594</v>
+        <v>0.06959435841286037</v>
       </c>
       <c r="Y4">
-        <v>0.125483935016198</v>
+        <v>0.2184173374935723</v>
       </c>
       <c r="Z4">
-        <v>0.461864406779661</v>
+        <v>1.927827897293546</v>
       </c>
       <c r="AA4">
-        <v>0.3187134225127308</v>
+        <v>0.2887142873945823</v>
       </c>
       <c r="AB4">
-        <v>0.07573575604237995</v>
+        <v>0.06755036550793454</v>
       </c>
       <c r="AC4">
-        <v>0.2429776664703509</v>
+        <v>0.2211639218866478</v>
       </c>
       <c r="AD4">
-        <v>326.3</v>
+        <v>27</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>326.3</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>292.1</v>
+        <v>11.1</v>
       </c>
       <c r="AH4">
-        <v>0.7190392243278978</v>
+        <v>0.08335906143871566</v>
       </c>
       <c r="AI4">
-        <v>0.4404103117829666</v>
+        <v>0.1664611590628853</v>
       </c>
       <c r="AJ4">
-        <v>0.696139180171592</v>
+        <v>0.03603896103896104</v>
       </c>
       <c r="AK4">
-        <v>0.4133295599264186</v>
+        <v>0.07587149692412851</v>
       </c>
       <c r="AL4">
-        <v>9.44</v>
+        <v>3.34</v>
       </c>
       <c r="AM4">
-        <v>8.719999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="AN4">
-        <v>4.109571788413098</v>
+        <v>0.4173106646058732</v>
       </c>
       <c r="AO4">
-        <v>8.411016949152543</v>
+        <v>18.65269461077844</v>
       </c>
       <c r="AP4">
-        <v>3.678841309823678</v>
+        <v>0.1715610510046368</v>
       </c>
       <c r="AQ4">
-        <v>9.105504587155965</v>
+        <v>18.65269461077844</v>
       </c>
     </row>
     <row r="5">
@@ -975,46 +960,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.283</v>
+        <v>0.292</v>
       </c>
       <c r="E5">
-        <v>0.194</v>
+        <v>0.0886</v>
       </c>
       <c r="G5">
-        <v>0.114828897338403</v>
+        <v>0.1302992518703242</v>
       </c>
       <c r="H5">
-        <v>0.114828897338403</v>
+        <v>0.1302992518703242</v>
       </c>
       <c r="I5">
-        <v>0.1429657794676806</v>
+        <v>0.1608478802992519</v>
       </c>
       <c r="J5">
-        <v>0.08927915082382763</v>
+        <v>0.1069298584524604</v>
       </c>
       <c r="K5">
-        <v>11.2</v>
+        <v>16.7</v>
       </c>
       <c r="L5">
-        <v>0.08517110266159696</v>
+        <v>0.1041147132169576</v>
       </c>
       <c r="M5">
-        <v>6.08</v>
+        <v>14.5</v>
       </c>
       <c r="N5">
-        <v>0.03210137275607181</v>
+        <v>0.08972772277227722</v>
       </c>
       <c r="O5">
-        <v>0.5428571428571429</v>
+        <v>0.8682634730538923</v>
       </c>
       <c r="P5">
-        <v>6.08</v>
+        <v>14.5</v>
       </c>
       <c r="Q5">
-        <v>0.03210137275607181</v>
+        <v>0.08972772277227722</v>
       </c>
       <c r="R5">
-        <v>0.5428571428571429</v>
+        <v>0.8682634730538923</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,73 +1008,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>43.7</v>
+        <v>20.8</v>
       </c>
       <c r="V5">
-        <v>0.2307286166842661</v>
+        <v>0.1287128712871287</v>
       </c>
       <c r="W5">
-        <v>0.3137254901960784</v>
+        <v>0.2420289855072464</v>
       </c>
       <c r="X5">
-        <v>0.0857813857808791</v>
+        <v>0.07679416374839071</v>
       </c>
       <c r="Y5">
-        <v>0.2279441044151993</v>
+        <v>0.1652348217588556</v>
       </c>
       <c r="Z5">
-        <v>2.543520309477756</v>
+        <v>2.502340093603745</v>
       </c>
       <c r="AA5">
-        <v>0.2270833333333334</v>
+        <v>0.2675748720089648</v>
       </c>
       <c r="AB5">
-        <v>0.07851845990929961</v>
+        <v>0.06747775609997803</v>
       </c>
       <c r="AC5">
-        <v>0.1485648734240338</v>
+        <v>0.2000971159089868</v>
       </c>
       <c r="AD5">
-        <v>38.8</v>
+        <v>67.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>38.8</v>
+        <v>67.2</v>
       </c>
       <c r="AG5">
-        <v>-4.900000000000006</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.1700262927256792</v>
+        <v>0.2937062937062937</v>
       </c>
       <c r="AI5">
-        <v>0.3154471544715447</v>
+        <v>0.4477015323117921</v>
       </c>
       <c r="AJ5">
-        <v>-0.02655826558265586</v>
+        <v>0.2230769230769231</v>
       </c>
       <c r="AK5">
-        <v>-0.06179066834804547</v>
+        <v>0.3588553750966744</v>
       </c>
       <c r="AL5">
-        <v>1.13</v>
+        <v>2.67</v>
       </c>
       <c r="AM5">
-        <v>0.6339999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="AN5">
-        <v>1.911330049261084</v>
+        <v>2.443636363636364</v>
       </c>
       <c r="AO5">
-        <v>16.63716814159292</v>
+        <v>9.662921348314608</v>
       </c>
       <c r="AP5">
-        <v>-0.2413793103448278</v>
+        <v>1.687272727272727</v>
       </c>
       <c r="AQ5">
-        <v>29.65299684542587</v>
+        <v>49.61538461538461</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Generation Capital Ltd (TASE:GNRS)</t>
+          <t>Keystone Infra Ltd (TASE:KSTN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,40 +1094,40 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.5140712945590994</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.5140712945590994</v>
       </c>
       <c r="I6">
-        <v>0.8797423049391554</v>
+        <v>0.9118198874296436</v>
       </c>
       <c r="J6">
-        <v>0.7026072936363775</v>
+        <v>0.7370730785364933</v>
       </c>
       <c r="K6">
-        <v>82.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="L6">
-        <v>0.5934144595561919</v>
+        <v>0.6172607879924953</v>
       </c>
       <c r="M6">
-        <v>15.18</v>
+        <v>7.87</v>
       </c>
       <c r="N6">
-        <v>0.037060546875</v>
+        <v>0.03541854185418542</v>
       </c>
       <c r="O6">
-        <v>0.1831121833534379</v>
+        <v>0.1196048632218845</v>
       </c>
       <c r="P6">
-        <v>15.18</v>
+        <v>7.87</v>
       </c>
       <c r="Q6">
-        <v>0.037060546875</v>
+        <v>0.03541854185418542</v>
       </c>
       <c r="R6">
-        <v>0.1831121833534379</v>
+        <v>0.1196048632218845</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,67 +1136,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>90.09999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="V6">
-        <v>0.219970703125</v>
+        <v>0.1300630063006301</v>
       </c>
       <c r="W6">
-        <v>0.1667001809772773</v>
+        <v>0.1587071876507477</v>
       </c>
       <c r="X6">
-        <v>0.1108024970669028</v>
+        <v>0.09534388671239427</v>
       </c>
       <c r="Y6">
-        <v>0.05589768391037454</v>
+        <v>0.06336330093835343</v>
       </c>
       <c r="Z6">
-        <v>0.2534930139720559</v>
+        <v>0.1508419414178576</v>
       </c>
       <c r="AA6">
-        <v>0.1781060405026346</v>
+        <v>0.1111815341332817</v>
       </c>
       <c r="AB6">
-        <v>0.07683887368315701</v>
+        <v>0.0648983425502466</v>
       </c>
       <c r="AC6">
-        <v>0.1012671668194776</v>
+        <v>0.04628319158303509</v>
       </c>
       <c r="AD6">
-        <v>411.9</v>
+        <v>278.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>411.9</v>
+        <v>278.4</v>
       </c>
       <c r="AG6">
-        <v>321.8</v>
+        <v>249.5</v>
       </c>
       <c r="AH6">
-        <v>0.5013998782714546</v>
+        <v>0.5561326408310028</v>
       </c>
       <c r="AI6">
-        <v>0.4347229551451187</v>
+        <v>0.386881600889383</v>
       </c>
       <c r="AJ6">
-        <v>0.4399781241454744</v>
+        <v>0.528937884248463</v>
       </c>
       <c r="AK6">
-        <v>0.3753207371121997</v>
+        <v>0.3612277399739395</v>
       </c>
       <c r="AL6">
-        <v>17.2</v>
+        <v>9.42</v>
       </c>
       <c r="AM6">
-        <v>16.966</v>
+        <v>7.77</v>
+      </c>
+      <c r="AN6">
+        <v>2.864197530864197</v>
       </c>
       <c r="AO6">
-        <v>7.145348837209303</v>
+        <v>10.31847133757962</v>
+      </c>
+      <c r="AP6">
+        <v>2.566872427983539</v>
       </c>
       <c r="AQ6">
-        <v>7.243899563833551</v>
+        <v>12.50965250965251</v>
       </c>
     </row>
     <row r="7">
@@ -1222,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital Point Ltd. (TASE:CPTP)</t>
+          <t>Analyst I.M.S. Investment Management Services Ltd (TASE:ANLT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,121 +1222,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.04849999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="E7">
-        <v>-0.0636</v>
+        <v>-0.039</v>
       </c>
       <c r="G7">
-        <v>1.419558359621451</v>
+        <v>0.1182952182952183</v>
       </c>
       <c r="H7">
-        <v>1.419558359621451</v>
+        <v>0.1182952182952183</v>
       </c>
       <c r="I7">
-        <v>0.6203995793901157</v>
+        <v>0.1604989604989605</v>
       </c>
       <c r="J7">
-        <v>0.4471348319928762</v>
+        <v>0.08024948024948024</v>
       </c>
       <c r="K7">
-        <v>0.16</v>
+        <v>3.91</v>
       </c>
       <c r="L7">
-        <v>0.01682439537329127</v>
+        <v>0.08128898128898129</v>
       </c>
       <c r="M7">
-        <v>9.109999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="N7">
-        <v>0.3960869565217391</v>
+        <v>0.01306005719733079</v>
       </c>
       <c r="O7">
-        <v>56.93749999999999</v>
+        <v>0.350383631713555</v>
       </c>
       <c r="P7">
-        <v>3.6</v>
+        <v>1.37</v>
       </c>
       <c r="Q7">
-        <v>0.1565217391304348</v>
+        <v>0.01306005719733079</v>
       </c>
       <c r="R7">
-        <v>22.5</v>
+        <v>0.350383631713555</v>
       </c>
       <c r="S7">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.6048298572996708</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>5.09</v>
+        <v>4.9</v>
       </c>
       <c r="V7">
-        <v>0.221304347826087</v>
+        <v>0.04671115347950429</v>
       </c>
       <c r="W7">
-        <v>0.002935779816513761</v>
+        <v>0.0851851851851852</v>
       </c>
       <c r="X7">
-        <v>0.08670286556839511</v>
+        <v>0.06857623166214905</v>
       </c>
       <c r="Y7">
-        <v>-0.08376708575188135</v>
+        <v>0.01660895352303615</v>
       </c>
       <c r="Z7">
-        <v>0.2250887573964497</v>
+        <v>1.249675240322162</v>
       </c>
       <c r="AA7">
-        <v>0.1006450237219468</v>
+        <v>0.1002857885164978</v>
       </c>
       <c r="AB7">
-        <v>0.0795436077537208</v>
+        <v>0.06737158286952429</v>
       </c>
       <c r="AC7">
-        <v>0.021101415968226</v>
+        <v>0.03291420564697352</v>
       </c>
       <c r="AD7">
-        <v>5.39</v>
+        <v>4.72</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5.39</v>
+        <v>4.72</v>
       </c>
       <c r="AG7">
-        <v>0.2999999999999998</v>
+        <v>-0.1800000000000006</v>
       </c>
       <c r="AH7">
-        <v>0.1898555829517436</v>
+        <v>0.04305783616128443</v>
       </c>
       <c r="AI7">
-        <v>0.1046805204894154</v>
+        <v>0.092151503319016</v>
       </c>
       <c r="AJ7">
-        <v>0.01287553648068669</v>
+        <v>-0.001718869365928195</v>
       </c>
       <c r="AK7">
-        <v>0.006465517241379307</v>
+        <v>-0.003886010362694313</v>
       </c>
       <c r="AL7">
-        <v>0.312</v>
+        <v>0.231</v>
       </c>
       <c r="AM7">
-        <v>0.312</v>
+        <v>0.007000000000000006</v>
       </c>
       <c r="AN7">
-        <v>0.9120135363790185</v>
+        <v>0.5209713024282561</v>
       </c>
       <c r="AO7">
-        <v>18.91025641025641</v>
+        <v>33.41991341991342</v>
       </c>
       <c r="AP7">
-        <v>0.05076142131979693</v>
+        <v>-0.01986754966887424</v>
       </c>
       <c r="AQ7">
-        <v>18.91025641025641</v>
+        <v>1102.857142857142</v>
       </c>
     </row>
     <row r="8">
@@ -1365,121 +1356,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.403</v>
+        <v>0.357</v>
       </c>
       <c r="E8">
-        <v>0.528</v>
+        <v>0.327</v>
       </c>
       <c r="G8">
-        <v>0.6639004149377593</v>
+        <v>0.6480938416422287</v>
       </c>
       <c r="H8">
-        <v>0.6639004149377593</v>
+        <v>0.6480938416422287</v>
       </c>
       <c r="I8">
-        <v>0.8506224066390041</v>
+        <v>0.7595307917888562</v>
       </c>
       <c r="J8">
-        <v>0.6475280645887612</v>
+        <v>0.5801054018445322</v>
       </c>
       <c r="K8">
-        <v>9.83</v>
+        <v>10.5</v>
       </c>
       <c r="L8">
-        <v>0.4078838174273859</v>
+        <v>0.3079178885630499</v>
       </c>
       <c r="M8">
-        <v>1.486</v>
+        <v>3.2</v>
       </c>
       <c r="N8">
-        <v>0.02321875</v>
+        <v>0.0539629005059022</v>
       </c>
       <c r="O8">
-        <v>0.1511698880976602</v>
+        <v>0.3047619047619048</v>
       </c>
       <c r="P8">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Q8">
-        <v>0.021875</v>
+        <v>0.02209106239460371</v>
       </c>
       <c r="R8">
-        <v>0.1424211597151577</v>
+        <v>0.1247619047619048</v>
       </c>
       <c r="S8">
-        <v>0.08600000000000008</v>
+        <v>1.89</v>
       </c>
       <c r="T8">
-        <v>0.05787348586810234</v>
+        <v>0.590625</v>
       </c>
       <c r="U8">
-        <v>14.1</v>
+        <v>26.5</v>
       </c>
       <c r="V8">
-        <v>0.2203125</v>
+        <v>0.4468802698145026</v>
       </c>
       <c r="W8">
-        <v>0.2769014084507042</v>
+        <v>0.2567237163814181</v>
       </c>
       <c r="X8">
-        <v>0.1682871329972423</v>
+        <v>0.1463534217285256</v>
       </c>
       <c r="Y8">
-        <v>0.1086142754534619</v>
+        <v>0.1103702946528925</v>
       </c>
       <c r="Z8">
-        <v>0.1428825517282267</v>
+        <v>0.1632359980852082</v>
       </c>
       <c r="AA8">
-        <v>0.09252046218408222</v>
+        <v>0.09469408426471301</v>
       </c>
       <c r="AB8">
-        <v>0.07562980347321936</v>
+        <v>0.06730973727570097</v>
       </c>
       <c r="AC8">
-        <v>0.01689065871086286</v>
+        <v>0.02738434698901204</v>
       </c>
       <c r="AD8">
-        <v>182.1</v>
+        <v>210.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>182.1</v>
+        <v>210.8</v>
       </c>
       <c r="AG8">
-        <v>168</v>
+        <v>184.3</v>
       </c>
       <c r="AH8">
-        <v>0.7399431125558716</v>
+        <v>0.7804516845612736</v>
       </c>
       <c r="AI8">
-        <v>0.816591928251121</v>
+        <v>0.8215120810600156</v>
       </c>
       <c r="AJ8">
-        <v>0.7241379310344828</v>
+        <v>0.756568144499179</v>
       </c>
       <c r="AK8">
-        <v>0.8042125418860698</v>
+        <v>0.8009561060408518</v>
       </c>
       <c r="AL8">
-        <v>6.78</v>
+        <v>10.5</v>
       </c>
       <c r="AM8">
-        <v>6.78</v>
+        <v>10.5</v>
       </c>
       <c r="AN8">
-        <v>8.839805825242717</v>
+        <v>8.107692307692307</v>
       </c>
       <c r="AO8">
-        <v>3.023598820058997</v>
+        <v>2.466666666666666</v>
       </c>
       <c r="AP8">
-        <v>8.155339805825243</v>
+        <v>7.088461538461539</v>
       </c>
       <c r="AQ8">
-        <v>3.023598820058997</v>
+        <v>2.466666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1481,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meitav Investment House Ltd (TASE:MTAV)</t>
+          <t>Generation Capital Ltd (TASE:GNRS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1498,47 +1489,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0638</v>
-      </c>
-      <c r="E9">
-        <v>0.022</v>
-      </c>
       <c r="G9">
-        <v>0.3629652414641649</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0.3629652414641649</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.2537680713626576</v>
+        <v>0.836082474226804</v>
       </c>
       <c r="J9">
-        <v>0.1526354082365801</v>
+        <v>0.7158770224162601</v>
       </c>
       <c r="K9">
-        <v>27.2</v>
+        <v>48.1</v>
       </c>
       <c r="L9">
-        <v>0.08366656413411257</v>
+        <v>0.4958762886597938</v>
       </c>
       <c r="M9">
-        <v>7.1797</v>
+        <v>14.4</v>
       </c>
       <c r="N9">
-        <v>0.03330102040816326</v>
+        <v>0.05901639344262295</v>
       </c>
       <c r="O9">
-        <v>0.2639595588235294</v>
+        <v>0.2993762993762994</v>
       </c>
       <c r="P9">
-        <v>7.1797</v>
+        <v>14.4</v>
       </c>
       <c r="Q9">
-        <v>0.03330102040816326</v>
+        <v>0.05901639344262295</v>
       </c>
       <c r="R9">
-        <v>0.2639595588235294</v>
+        <v>0.2993762993762994</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1547,70 +1532,67 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>82</v>
+        <v>38.1</v>
       </c>
       <c r="V9">
-        <v>0.3803339517625232</v>
+        <v>0.1561475409836066</v>
       </c>
       <c r="W9">
-        <v>0.1851599727705922</v>
+        <v>0.08980582524271845</v>
       </c>
       <c r="X9">
-        <v>0.1908310006530669</v>
+        <v>0.1078666336734927</v>
       </c>
       <c r="Y9">
-        <v>-0.005671027882474616</v>
+        <v>-0.01806080843077422</v>
       </c>
       <c r="Z9">
-        <v>0.5216623876765084</v>
+        <v>0.1131327268486121</v>
       </c>
       <c r="AA9">
-        <v>0.07962415150467296</v>
+        <v>0.0809891196342165</v>
       </c>
       <c r="AB9">
-        <v>0.07542156320871077</v>
+        <v>0.06735644441741605</v>
       </c>
       <c r="AC9">
-        <v>0.004202588295962192</v>
+        <v>0.01363267521680045</v>
       </c>
       <c r="AD9">
-        <v>769</v>
+        <v>443.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>769</v>
+        <v>443.6</v>
       </c>
       <c r="AG9">
-        <v>687</v>
+        <v>405.5</v>
       </c>
       <c r="AH9">
-        <v>0.7810278285598212</v>
+        <v>0.6451425247236766</v>
       </c>
       <c r="AI9">
-        <v>0.7879905728045906</v>
+        <v>0.4529766159501685</v>
       </c>
       <c r="AJ9">
-        <v>0.7611345003323732</v>
+        <v>0.6243264049268669</v>
       </c>
       <c r="AK9">
-        <v>0.7685423425439087</v>
+        <v>0.4308329791755206</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="AM9">
-        <v>-39</v>
-      </c>
-      <c r="AN9">
-        <v>8.478500551267915</v>
-      </c>
-      <c r="AP9">
-        <v>7.574421168687982</v>
+        <v>7.49</v>
+      </c>
+      <c r="AO9">
+        <v>9.3757225433526</v>
       </c>
       <c r="AQ9">
-        <v>-2.115384615384615</v>
+        <v>10.82777036048064</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unicorn Technologies - Limited Partnership (TASE:UNCT)</t>
+          <t>Meitav Investment House Ltd (TASE:MTAV)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1629,107 +1611,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.078</v>
+      </c>
+      <c r="E10">
+        <v>0.0585</v>
+      </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.3091659298555851</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.3091659298555851</v>
       </c>
       <c r="I10">
-        <v>0.3712418300653594</v>
+        <v>0.3197760094311818</v>
       </c>
       <c r="J10">
-        <v>0.3712418300653594</v>
+        <v>0.1788845993352651</v>
       </c>
       <c r="K10">
-        <v>0.5659999999999999</v>
+        <v>26.5</v>
       </c>
       <c r="L10">
-        <v>0.3699346405228758</v>
+        <v>0.07810197465369879</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>2.62</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.008026960784313726</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.09886792452830188</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>2.62</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.008026960784313726</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.09886792452830188</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>8.91</v>
+        <v>102.8</v>
       </c>
       <c r="V10">
-        <v>2.819620253164557</v>
+        <v>0.3149509803921569</v>
       </c>
       <c r="W10">
-        <v>0.02788177339901477</v>
+        <v>0.1949963208241354</v>
       </c>
       <c r="X10">
-        <v>0.07938024802941726</v>
+        <v>0.1151917761842311</v>
       </c>
       <c r="Y10">
-        <v>-0.05149847463040248</v>
+        <v>0.07980454463990425</v>
       </c>
       <c r="Z10">
-        <v>0.2095890410958904</v>
+        <v>0.4123222748815166</v>
       </c>
       <c r="AA10">
-        <v>0.07780821917808217</v>
+        <v>0.07375810493918514</v>
       </c>
       <c r="AB10">
-        <v>0.07938024802941726</v>
+        <v>0.06734358440506977</v>
       </c>
       <c r="AC10">
-        <v>-0.001572028851335089</v>
+        <v>0.00641452053411537</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>701.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>701.3</v>
       </c>
       <c r="AG10">
-        <v>-8.91</v>
+        <v>598.5</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.6823975868444099</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.7418024116775968</v>
       </c>
       <c r="AJ10">
-        <v>1.549565217391304</v>
+        <v>0.6470969834576711</v>
       </c>
       <c r="AK10">
-        <v>-0.891891891891892</v>
+        <v>0.7103014478993591</v>
       </c>
       <c r="AL10">
-        <v>0.002</v>
+        <v>42.7</v>
       </c>
       <c r="AM10">
-        <v>0.002</v>
+        <v>33</v>
+      </c>
+      <c r="AN10">
+        <v>6.024914089347078</v>
       </c>
       <c r="AO10">
-        <v>283.9999999999999</v>
+        <v>2.540983606557377</v>
+      </c>
+      <c r="AP10">
+        <v>5.141752577319587</v>
       </c>
       <c r="AQ10">
-        <v>283.9999999999999</v>
+        <v>3.287878787878788</v>
       </c>
     </row>
     <row r="11">
@@ -1740,7 +1737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Analyst I.M.S. Investment Management Services Ltd (TASE:ANLT)</t>
+          <t>The Trendlines Group Ltd. (Catalist:42T)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1749,121 +1746,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.09630000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="E11">
-        <v>-0.301</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G11">
-        <v>0.1462264150943396</v>
+        <v>-0.4770408163265307</v>
       </c>
       <c r="H11">
-        <v>0.1462264150943396</v>
+        <v>-0.5510204081632653</v>
       </c>
       <c r="I11">
-        <v>0.1025943396226415</v>
+        <v>0.3540816326530612</v>
       </c>
       <c r="J11">
-        <v>0.05129716981132075</v>
+        <v>0.2524259381171823</v>
       </c>
       <c r="K11">
-        <v>0.273</v>
+        <v>1.88</v>
       </c>
       <c r="L11">
-        <v>0.00643867924528302</v>
+        <v>0.09591836734693876</v>
       </c>
       <c r="M11">
-        <v>1.47</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.01501532175689479</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>5.384615384615384</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>1.47</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.01501532175689479</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>5.384615384615384</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>13</v>
+        <v>4.57</v>
       </c>
       <c r="V11">
-        <v>0.1327885597548519</v>
+        <v>0.06903323262839879</v>
       </c>
       <c r="W11">
-        <v>0.005438247011952191</v>
+        <v>0.01981032665964173</v>
       </c>
       <c r="X11">
-        <v>0.08116441106918254</v>
+        <v>0.06919594521654777</v>
       </c>
       <c r="Y11">
-        <v>-0.07572616405723034</v>
+        <v>-0.04938561855690605</v>
       </c>
       <c r="Z11">
-        <v>1.037181996086106</v>
+        <v>0.2169581580695152</v>
       </c>
       <c r="AA11">
-        <v>0.05320450097847357</v>
+        <v>0.0547658665828733</v>
       </c>
       <c r="AB11">
-        <v>0.07910647047583855</v>
+        <v>0.06725135367115365</v>
       </c>
       <c r="AC11">
-        <v>-0.02590196949736497</v>
+        <v>-0.01248548708828034</v>
       </c>
       <c r="AD11">
-        <v>5.59</v>
+        <v>4.83</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>5.59</v>
+        <v>4.83</v>
       </c>
       <c r="AG11">
-        <v>-7.41</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="AH11">
-        <v>0.05401488066479852</v>
+        <v>0.06799943685766577</v>
       </c>
       <c r="AI11">
-        <v>0.1085647698582249</v>
+        <v>0.04434040209308731</v>
       </c>
       <c r="AJ11">
-        <v>-0.08188750138136811</v>
+        <v>0.003912127595546189</v>
       </c>
       <c r="AK11">
-        <v>-0.1925175370226033</v>
+        <v>0.002491376006132616</v>
       </c>
       <c r="AL11">
-        <v>0.256</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.169</v>
+        <v>-0.776</v>
       </c>
       <c r="AN11">
-        <v>1.025688073394495</v>
-      </c>
-      <c r="AO11">
-        <v>16.9921875</v>
+        <v>0.6745810055865922</v>
       </c>
       <c r="AP11">
-        <v>-1.359633027522936</v>
+        <v>0.03631284916201114</v>
       </c>
       <c r="AQ11">
-        <v>25.7396449704142</v>
+        <v>-8.943298969072165</v>
       </c>
     </row>
     <row r="12">
@@ -1874,7 +1865,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Almeda Ventures Limited Partnership (TASE:AMDA)</t>
+          <t>Capital Point Ltd. (TASE:CPTP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1882,8 +1873,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>-0.0848</v>
+      </c>
+      <c r="G12">
+        <v>-0.2275042444821732</v>
+      </c>
+      <c r="H12">
+        <v>-0.2275042444821732</v>
+      </c>
+      <c r="I12">
+        <v>0.4091680814940578</v>
+      </c>
+      <c r="J12">
+        <v>0.4091680814940578</v>
+      </c>
       <c r="K12">
-        <v>0</v>
+        <v>-4.09</v>
+      </c>
+      <c r="L12">
+        <v>-0.6943972835314092</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1891,71 +1900,86 @@
       <c r="N12">
         <v>-0</v>
       </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
       <c r="P12">
         <v>-0</v>
       </c>
       <c r="Q12">
         <v>-0</v>
       </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.44</v>
+        <v>7.11</v>
       </c>
       <c r="V12">
-        <v>1.387931034482759</v>
+        <v>0.2662921348314607</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>-0.08872017353579176</v>
       </c>
       <c r="X12">
-        <v>0.08048466046932132</v>
+        <v>0.07279129026152029</v>
       </c>
       <c r="Y12">
-        <v>-0.08048466046932132</v>
+        <v>-0.161511463797312</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>0.1269396551724138</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.05193965517241379</v>
       </c>
       <c r="AB12">
-        <v>0.07950951041365367</v>
+        <v>0.06751340986237249</v>
       </c>
       <c r="AC12">
-        <v>-0.07950951041365367</v>
+        <v>-0.0155737546899587</v>
       </c>
       <c r="AD12">
-        <v>0.164</v>
+        <v>6.28</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.164</v>
+        <v>6.28</v>
       </c>
       <c r="AG12">
-        <v>-6.276000000000001</v>
+        <v>-0.8300000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.03413821815154039</v>
+        <v>0.1904184354154033</v>
       </c>
       <c r="AI12">
-        <v>0.005928282244071718</v>
+        <v>0.1351118760757315</v>
       </c>
       <c r="AJ12">
-        <v>3.836185819070903</v>
+        <v>-0.03208349439505219</v>
       </c>
       <c r="AK12">
-        <v>-0.2957029777610253</v>
+        <v>-0.02108204216408433</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>-0.006</v>
+      </c>
+      <c r="AN12">
+        <v>2.59504132231405</v>
+      </c>
+      <c r="AP12">
+        <v>-0.3429752066115703</v>
+      </c>
+      <c r="AQ12">
+        <v>-401.6666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -1975,121 +1999,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.245</v>
+        <v>-0.101</v>
       </c>
       <c r="E13">
-        <v>0.0646</v>
+        <v>0.28</v>
       </c>
       <c r="G13">
-        <v>1.326797385620915</v>
+        <v>0.1540760869565217</v>
       </c>
       <c r="H13">
-        <v>1.326797385620915</v>
+        <v>0.1540760869565217</v>
       </c>
       <c r="I13">
-        <v>-0.2464052287581699</v>
+        <v>0.5434782608695652</v>
       </c>
       <c r="J13">
-        <v>-0.1764720374476472</v>
+        <v>0.4095268542199488</v>
       </c>
       <c r="K13">
-        <v>6.46</v>
+        <v>1.28</v>
       </c>
       <c r="L13">
-        <v>4.222222222222222</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="M13">
-        <v>0.453</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.02031390134529148</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.07012383900928792</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.453</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.02031390134529148</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.07012383900928792</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>0.2735426008968609</v>
+        <v>0.1016949152542373</v>
       </c>
       <c r="W13">
-        <v>0.2243055555555555</v>
+        <v>0.03902439024390245</v>
       </c>
       <c r="X13">
-        <v>0.1544846424989289</v>
+        <v>0.13017783461192</v>
       </c>
       <c r="Y13">
-        <v>0.06982091305662663</v>
+        <v>-0.09115344436801756</v>
       </c>
       <c r="Z13">
-        <v>0.03192155226371792</v>
+        <v>0.04655281467425679</v>
       </c>
       <c r="AA13">
-        <v>-0.005633261366469856</v>
+        <v>0.01906462774863266</v>
       </c>
       <c r="AB13">
-        <v>0.08205420446049808</v>
+        <v>0.0688420216768556</v>
       </c>
       <c r="AC13">
-        <v>-0.08768746582696793</v>
+        <v>-0.04977739392822295</v>
       </c>
       <c r="AD13">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="AG13">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="AH13">
-        <v>0.7061923583662714</v>
+        <v>0.7385524372230428</v>
       </c>
       <c r="AI13">
-        <v>0.6203703703703703</v>
+        <v>0.6082725060827251</v>
       </c>
       <c r="AJ13">
-        <v>0.6805157593123209</v>
+        <v>0.7314112291350531</v>
       </c>
       <c r="AK13">
-        <v>0.5915317559153176</v>
+        <v>0.599502487562189</v>
       </c>
       <c r="AL13">
-        <v>0.839</v>
+        <v>3.07</v>
       </c>
       <c r="AM13">
-        <v>0.839</v>
+        <v>3.07</v>
       </c>
       <c r="AN13">
-        <v>-261.4634146341464</v>
+        <v>22.93577981651376</v>
       </c>
       <c r="AO13">
-        <v>-0.4493444576877235</v>
+        <v>0.6514657980456027</v>
       </c>
       <c r="AP13">
-        <v>-231.7073170731707</v>
+        <v>22.11009174311927</v>
       </c>
       <c r="AQ13">
-        <v>-0.4493444576877235</v>
+        <v>0.6514657980456027</v>
       </c>
     </row>
     <row r="14">
@@ -2100,7 +2121,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ybox Real Estate Ltd. (TASE:YBOX)</t>
+          <t>Eldav Investments Ltd. (TASE:ELDAV-M)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2108,113 +2129,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.6759999999999999</v>
+      </c>
       <c r="G14">
-        <v>0.04506437768240344</v>
+        <v>-3.35</v>
       </c>
       <c r="H14">
-        <v>0.04506437768240344</v>
+        <v>-3.35</v>
       </c>
       <c r="I14">
-        <v>-0.07296137339055793</v>
+        <v>-0.6357142857142857</v>
       </c>
       <c r="J14">
-        <v>-0.05366191333241035</v>
+        <v>-0.6357142857142857</v>
       </c>
       <c r="K14">
-        <v>11.4</v>
+        <v>-6.86</v>
       </c>
       <c r="L14">
-        <v>0.2446351931330472</v>
+        <v>-49</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>1.48</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.07326732673267326</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>-0.2157434402332361</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>1.48</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.07326732673267326</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>-0.2157434402332361</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>5.97</v>
+        <v>0.081</v>
       </c>
       <c r="V14">
-        <v>0.09328125</v>
+        <v>0.00400990099009901</v>
       </c>
       <c r="W14">
-        <v>0.1610169491525424</v>
+        <v>-0.145031712473573</v>
       </c>
       <c r="X14">
-        <v>0.1714606352064178</v>
+        <v>0.06764934978652366</v>
       </c>
       <c r="Y14">
-        <v>-0.01044368605387544</v>
+        <v>-0.2126810622600966</v>
       </c>
       <c r="Z14">
-        <v>0.2540755683986697</v>
+        <v>0.003819918144611187</v>
       </c>
       <c r="AA14">
-        <v>-0.01363418113129231</v>
+        <v>-0.00242837653478854</v>
       </c>
       <c r="AB14">
-        <v>0.08002268416541258</v>
+        <v>0.06756391567396565</v>
       </c>
       <c r="AC14">
-        <v>-0.09365686529670489</v>
+        <v>-0.06999229220875419</v>
       </c>
       <c r="AD14">
-        <v>188.6</v>
+        <v>0.064</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>188.6</v>
+        <v>0.064</v>
       </c>
       <c r="AG14">
-        <v>182.63</v>
+        <v>-0.017</v>
       </c>
       <c r="AH14">
-        <v>0.7466349960411718</v>
+        <v>0.003158310303987367</v>
       </c>
       <c r="AI14">
-        <v>0.6735714285714286</v>
+        <v>0.002240582551463381</v>
       </c>
       <c r="AJ14">
-        <v>0.7405019665085351</v>
+        <v>-0.000842293018877273</v>
       </c>
       <c r="AK14">
-        <v>0.6664598766558406</v>
+        <v>-0.0005968472422146544</v>
       </c>
       <c r="AL14">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="AM14">
-        <v>4.365</v>
+        <v>3.06</v>
       </c>
       <c r="AN14">
-        <v>-56.80722891566265</v>
+        <v>-0.7901234567901234</v>
       </c>
       <c r="AO14">
-        <v>-0.7709750566893424</v>
+        <v>-0.02079439252336449</v>
       </c>
       <c r="AP14">
-        <v>-55.00903614457832</v>
+        <v>0.2098765432098766</v>
       </c>
       <c r="AQ14">
-        <v>-0.7789232531500572</v>
+        <v>-0.02908496732026143</v>
       </c>
     </row>
     <row r="15">
@@ -2225,7 +2252,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TechnoPlus Ventures Ltd. (TASE:TNPV)</t>
+          <t>Ybox Real Estate Ltd. (TASE:YBOX)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2233,119 +2260,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>-0.0208</v>
-      </c>
       <c r="G15">
-        <v>0.0748502994011976</v>
+        <v>-0.3459530026109661</v>
       </c>
       <c r="H15">
-        <v>0.0748502994011976</v>
+        <v>-0.3459530026109661</v>
       </c>
       <c r="I15">
-        <v>-0.3323353293413174</v>
+        <v>-0.6370757180156658</v>
       </c>
       <c r="J15">
-        <v>-0.3323353293413174</v>
+        <v>-0.5926892950391645</v>
       </c>
       <c r="K15">
-        <v>-0.304</v>
+        <v>6.81</v>
       </c>
       <c r="L15">
-        <v>-0.9101796407185628</v>
+        <v>0.8890339425587467</v>
       </c>
       <c r="M15">
-        <v>1.18146</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.2152021857923497</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>-3.886381578947368</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>1.18146</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.2152021857923497</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>-3.886381578947368</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>5.13</v>
+        <v>0.887</v>
       </c>
       <c r="V15">
-        <v>0.9344262295081966</v>
+        <v>0.01791919191919192</v>
       </c>
       <c r="W15">
-        <v>-0.06770601336302895</v>
+        <v>0.07450765864332604</v>
       </c>
       <c r="X15">
-        <v>0.08165688125219697</v>
+        <v>0.1608299493138466</v>
       </c>
       <c r="Y15">
-        <v>-0.1493628946152259</v>
+        <v>-0.08632229067052055</v>
       </c>
       <c r="Z15">
-        <v>0.1312893081761006</v>
+        <v>0.02795314381637047</v>
       </c>
       <c r="AA15">
-        <v>-0.04363207547169811</v>
+        <v>-0.01656752910265299</v>
       </c>
       <c r="AB15">
-        <v>0.07943868212352953</v>
+        <v>0.06730023113249053</v>
       </c>
       <c r="AC15">
-        <v>-0.1230707575952276</v>
+        <v>-0.08386776023514353</v>
       </c>
       <c r="AD15">
-        <v>0.4</v>
+        <v>208.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.4</v>
+        <v>208.3</v>
       </c>
       <c r="AG15">
-        <v>-4.73</v>
+        <v>207.413</v>
       </c>
       <c r="AH15">
-        <v>0.06791171477079797</v>
+        <v>0.8079906904577192</v>
       </c>
       <c r="AI15">
-        <v>0.05398110661268556</v>
+        <v>0.6906498673740052</v>
       </c>
       <c r="AJ15">
-        <v>-6.22368421052631</v>
+        <v>0.8073277724365836</v>
       </c>
       <c r="AK15">
-        <v>-2.074561403508771</v>
+        <v>0.6897373908011958</v>
       </c>
       <c r="AL15">
-        <v>0.321</v>
+        <v>2.41</v>
       </c>
       <c r="AM15">
-        <v>0.32</v>
+        <v>2.309</v>
       </c>
       <c r="AN15">
-        <v>-3.636363636363637</v>
+        <v>-43.48643006263048</v>
       </c>
       <c r="AO15">
-        <v>-0.3457943925233645</v>
+        <v>-2.024896265560166</v>
       </c>
       <c r="AP15">
-        <v>42.99999999999999</v>
+        <v>-43.30125260960335</v>
       </c>
       <c r="AQ15">
-        <v>-0.346875</v>
+        <v>-2.113469034213945</v>
       </c>
     </row>
     <row r="16">
@@ -2356,7 +2377,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eldav Investments Ltd. (TASE:ELDAV)</t>
+          <t>Almeda Ventures Limited Partnership (TASE:AMDA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2364,122 +2385,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>-0.7509999999999999</v>
-      </c>
-      <c r="E16">
-        <v>1.09</v>
-      </c>
       <c r="G16">
-        <v>-57.61904761904763</v>
+        <v>-1.256410256410256</v>
       </c>
       <c r="H16">
-        <v>-57.85714285714285</v>
+        <v>-1.256410256410256</v>
       </c>
       <c r="I16">
-        <v>-64.76190476190476</v>
+        <v>-1.970414201183432</v>
       </c>
       <c r="J16">
-        <v>-48.83809523809524</v>
+        <v>-1.970414201183432</v>
       </c>
       <c r="K16">
-        <v>12.9</v>
+        <v>-1</v>
       </c>
       <c r="L16">
-        <v>307.1428571428571</v>
+        <v>-1.972386587771203</v>
       </c>
       <c r="M16">
-        <v>3.957</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.1527799227799228</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.3067441860465116</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3.86</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.149034749034749</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.2992248062015504</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>0.09699999999999998</v>
-      </c>
-      <c r="T16">
-        <v>0.02451352034369471</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>13</v>
+        <v>3.96</v>
       </c>
       <c r="V16">
-        <v>0.5019305019305019</v>
+        <v>0.5625</v>
       </c>
       <c r="W16">
-        <v>0.3553719008264463</v>
+        <v>-0.03731343283582089</v>
       </c>
       <c r="X16">
-        <v>0.08221538157417521</v>
+        <v>0.0679159459561787</v>
       </c>
       <c r="Y16">
-        <v>0.2731565192522711</v>
+        <v>-0.1052293787919996</v>
       </c>
       <c r="Z16">
-        <v>0.001146914254505735</v>
+        <v>0.02690654354402165</v>
       </c>
       <c r="AA16">
-        <v>-0.05601310759148007</v>
+        <v>-0.05301703550390065</v>
       </c>
       <c r="AB16">
-        <v>0.07895861577398849</v>
+        <v>0.06760474016070619</v>
       </c>
       <c r="AC16">
-        <v>-0.1349717233654686</v>
+        <v>-0.1206217756646069</v>
       </c>
       <c r="AD16">
-        <v>2.35</v>
+        <v>0.107</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>2.35</v>
+        <v>0.107</v>
       </c>
       <c r="AG16">
-        <v>-10.65</v>
+        <v>-3.853</v>
       </c>
       <c r="AH16">
-        <v>0.0831858407079646</v>
+        <v>0.01497131663635091</v>
       </c>
       <c r="AI16">
-        <v>0.0473313192346425</v>
+        <v>0.00411427692544315</v>
       </c>
       <c r="AJ16">
-        <v>-0.698360655737705</v>
+        <v>-1.20897395669909</v>
       </c>
       <c r="AK16">
-        <v>-0.2905866302864939</v>
+        <v>-0.1747630063047127</v>
       </c>
       <c r="AL16">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>-0.638</v>
+        <v>-0.052</v>
       </c>
       <c r="AN16">
-        <v>-0.9670781893004115</v>
-      </c>
-      <c r="AO16">
-        <v>-24.28571428571429</v>
+        <v>-0.107</v>
       </c>
       <c r="AP16">
-        <v>4.382716049382716</v>
+        <v>3.853</v>
       </c>
       <c r="AQ16">
-        <v>4.263322884012539</v>
+        <v>19.21153846153846</v>
       </c>
     </row>
     <row r="17">
@@ -2490,7 +2499,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Trendlines Group Ltd. (Catalist:42T)</t>
+          <t>Unicorn Technologies - Limited Partnership (TASE:UNCT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2498,26 +2507,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>-0.542</v>
-      </c>
-      <c r="G17">
-        <v>32.30769230769231</v>
-      </c>
-      <c r="H17">
-        <v>20.6508875739645</v>
-      </c>
-      <c r="I17">
-        <v>-79.28994082840237</v>
-      </c>
-      <c r="J17">
-        <v>-79.28994082840237</v>
-      </c>
       <c r="K17">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="L17">
-        <v>-56.98224852071006</v>
+        <v>-3.58</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2541,73 +2532,67 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>9.720000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>0.1550239234449761</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="W17">
-        <v>-0.09553571428571429</v>
+        <v>-0.1894179894179894</v>
       </c>
       <c r="X17">
-        <v>0.08195175427296561</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y17">
-        <v>-0.1774874685586799</v>
+        <v>-0.2569971295003913</v>
       </c>
       <c r="Z17">
-        <v>0.001652973395931143</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>-0.1310641627543036</v>
+        <v>-0.08208208208208209</v>
       </c>
       <c r="AB17">
-        <v>0.0789948404388594</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="AC17">
-        <v>-0.210059003193163</v>
+        <v>-0.1496612221644839</v>
       </c>
       <c r="AD17">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-4.56</v>
+        <v>-2.75</v>
       </c>
       <c r="AH17">
-        <v>0.07603890362511052</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.05193236714975846</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-0.07843137254901962</v>
+        <v>-1.315789473684211</v>
       </c>
       <c r="AK17">
-        <v>-0.05087014725568943</v>
+        <v>-0.240174672489083</v>
       </c>
       <c r="AL17">
-        <v>1.52</v>
+        <v>0.007</v>
       </c>
       <c r="AM17">
-        <v>1.52</v>
-      </c>
-      <c r="AN17">
-        <v>-0.4</v>
+        <v>-0.178</v>
       </c>
       <c r="AO17">
-        <v>-8.815789473684211</v>
-      </c>
-      <c r="AP17">
-        <v>0.3534883720930233</v>
+        <v>-117.1428571428571</v>
       </c>
       <c r="AQ17">
-        <v>-8.815789473684211</v>
+        <v>4.606741573033708</v>
       </c>
     </row>
     <row r="18">
@@ -2618,7 +2603,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Feat Fund Investments - Limited Partnership (TASE:FEAT)</t>
+          <t>TechnoPlus Ventures Ltd. (TASE:TNPV)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2626,110 +2611,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.116</v>
+      </c>
       <c r="G18">
-        <v>-5.560344827586206</v>
+        <v>-6.432835820895522</v>
       </c>
       <c r="H18">
-        <v>-5.560344827586206</v>
+        <v>-6.432835820895522</v>
       </c>
       <c r="I18">
-        <v>-4.913793103448275</v>
+        <v>-4.26865671641791</v>
       </c>
       <c r="J18">
-        <v>-4.913793103448275</v>
+        <v>-4.26865671641791</v>
       </c>
       <c r="K18">
-        <v>-1.14</v>
+        <v>-0.578</v>
       </c>
       <c r="L18">
-        <v>-4.913793103448275</v>
+        <v>-8.62686567164179</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>1.45</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.3002070393374741</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-2.508650519031142</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.3002070393374741</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>-2.508650519031142</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>4.51</v>
+        <v>0.061</v>
       </c>
       <c r="V18">
-        <v>2.478021978021978</v>
+        <v>0.01262939958592132</v>
       </c>
       <c r="W18">
-        <v>-0.09743589743589744</v>
+        <v>-0.08245363766048502</v>
       </c>
       <c r="X18">
-        <v>0.07938024802941726</v>
+        <v>0.06933174800452145</v>
       </c>
       <c r="Y18">
-        <v>-0.1768161454653147</v>
+        <v>-0.1517853856650065</v>
       </c>
       <c r="Z18">
-        <v>0.09027237354085609</v>
+        <v>0.0293859649122807</v>
       </c>
       <c r="AA18">
-        <v>-0.4435797665369652</v>
+        <v>-0.125438596491228</v>
       </c>
       <c r="AB18">
-        <v>0.07938024802941726</v>
+        <v>0.06770446581558222</v>
       </c>
       <c r="AC18">
-        <v>-0.5229600145663824</v>
+        <v>-0.1931430623068103</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>0.382</v>
       </c>
       <c r="AG18">
-        <v>-4.51</v>
+        <v>0.321</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.07329240214888719</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.07124207385303991</v>
       </c>
       <c r="AJ18">
-        <v>1.676579925650558</v>
+        <v>0.06231799650553291</v>
       </c>
       <c r="AK18">
-        <v>-0.8525519848771265</v>
+        <v>0.06055461233729485</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.162</v>
       </c>
       <c r="AM18">
-        <v>-0.001</v>
+        <v>0.157</v>
       </c>
       <c r="AN18">
-        <v>-0</v>
+        <v>-1.335664335664336</v>
+      </c>
+      <c r="AO18">
+        <v>-1.765432098765432</v>
       </c>
       <c r="AP18">
-        <v>3.956140350877193</v>
+        <v>-1.122377622377623</v>
       </c>
       <c r="AQ18">
-        <v>1140</v>
+        <v>-1.821656050955414</v>
       </c>
     </row>
     <row r="19">
@@ -2740,7 +2734,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gesher I Acquisition Corp. (NasdaqGM:GIAC)</t>
+          <t>Big Tech 50 R&amp;D-Limited Partnership (TASE:BIGT)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2749,88 +2743,100 @@
         </is>
       </c>
       <c r="K19">
-        <v>-3</v>
+        <v>-5.85</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>3.418</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.553074433656958</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>-0.5842735042735043</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>2.61</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.4223300970873786</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>-0.4461538461538462</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>0.8080000000000003</v>
+      </c>
+      <c r="T19">
+        <v>0.2363955529549445</v>
       </c>
       <c r="U19">
-        <v>0.183</v>
+        <v>3.56</v>
       </c>
       <c r="V19">
-        <v>0.001232323232323232</v>
+        <v>0.5760517799352751</v>
       </c>
       <c r="W19">
-        <v>-300</v>
+        <v>-0.1822429906542056</v>
       </c>
       <c r="X19">
-        <v>0.07964747647755173</v>
+        <v>0.06764726934120532</v>
       </c>
       <c r="Y19">
-        <v>-300.0796474764775</v>
+        <v>-0.2498902599954109</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>-19.94623655913978</v>
+        <v>-0.2733485193621868</v>
       </c>
       <c r="AB19">
-        <v>0.07933726833645786</v>
+        <v>0.06758438107157734</v>
       </c>
       <c r="AC19">
-        <v>-20.02557382747624</v>
+        <v>-0.3409329004337641</v>
       </c>
       <c r="AD19">
-        <v>1.27</v>
+        <v>0.019</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.27</v>
+        <v>0.019</v>
       </c>
       <c r="AG19">
-        <v>1.087</v>
+        <v>-3.541</v>
       </c>
       <c r="AH19">
-        <v>0.008479668825532482</v>
+        <v>0.003065010485562188</v>
       </c>
       <c r="AI19">
-        <v>-0.2326007326007326</v>
+        <v>0.0008326394671107411</v>
       </c>
       <c r="AJ19">
-        <v>0.007266674243082621</v>
+        <v>-1.341796134899583</v>
       </c>
       <c r="AK19">
-        <v>-0.1926280347332979</v>
+        <v>-0.1838620904512176</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="AM19">
-        <v>-0.673</v>
+        <v>0.297</v>
+      </c>
+      <c r="AN19">
+        <v>-0.002996845425867508</v>
+      </c>
+      <c r="AO19">
+        <v>-21.41414141414142</v>
+      </c>
+      <c r="AP19">
+        <v>0.5585173501577287</v>
       </c>
       <c r="AQ19">
-        <v>5.512630014858841</v>
+        <v>-21.41414141414142</v>
       </c>
     </row>
     <row r="20">
@@ -2841,7 +2847,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Big Tech 50 R&amp;D-Limited Partnership (TASE:BIGT)</t>
+          <t>Feat Fund Investments - Limited Partnership (TASE:FEAT)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2849,86 +2855,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G20">
+        <v>-11.19565217391304</v>
+      </c>
+      <c r="H20">
+        <v>-25.65217391304348</v>
+      </c>
+      <c r="I20">
+        <v>-25.65217391304348</v>
+      </c>
+      <c r="J20">
+        <v>-25.65217391304348</v>
+      </c>
       <c r="K20">
-        <v>-2.75</v>
+        <v>-1.6</v>
+      </c>
+      <c r="L20">
+        <v>-34.78260869565218</v>
       </c>
       <c r="M20">
-        <v>3.853</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.5512160228898426</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>-1.401090909090909</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>3.57</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.5107296137339056</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>-1.298181818181818</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>0.2829999999999999</v>
-      </c>
-      <c r="T20">
-        <v>0.07344926031663637</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>6.1</v>
+        <v>3.52</v>
       </c>
       <c r="V20">
-        <v>0.8726752503576537</v>
+        <v>1.97752808988764</v>
       </c>
       <c r="W20">
-        <v>-1.131687242798354</v>
+        <v>-0.1391304347826087</v>
       </c>
       <c r="X20">
-        <v>0.07952776506839115</v>
+        <v>0.06757914008240185</v>
       </c>
       <c r="Y20">
-        <v>-1.211215007866745</v>
+        <v>-0.2067095748650105</v>
+      </c>
+      <c r="Z20">
+        <v>0.01277777777777778</v>
+      </c>
+      <c r="AA20">
+        <v>-0.3277777777777778</v>
       </c>
       <c r="AB20">
-        <v>0.07938429111459192</v>
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AC20">
+        <v>-0.3953569178601796</v>
       </c>
       <c r="AD20">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>-6.066999999999999</v>
+        <v>-3.52</v>
       </c>
       <c r="AH20">
-        <v>0.004698846646732166</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>0.001128861218485958</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-6.573131094257848</v>
+        <v>2.022988505747127</v>
       </c>
       <c r="AK20">
-        <v>-0.2622660268879955</v>
+        <v>-0.6874999999999999</v>
       </c>
       <c r="AL20">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>-0.046</v>
-      </c>
-      <c r="AO20">
-        <v>-226</v>
-      </c>
-      <c r="AQ20">
-        <v>73.69565217391305</v>
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>-0</v>
+      </c>
+      <c r="AP20">
+        <v>2.983050847457627</v>
       </c>
     </row>
     <row r="21">
@@ -2939,7 +2966,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mia Dynamics Motors Ltd (TASE:MIA)</t>
+          <t>Spring Ventures Ltd (TASE:SPRG)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2948,16 +2975,16 @@
         </is>
       </c>
       <c r="K21">
-        <v>-13.8</v>
+        <v>-19.5</v>
       </c>
       <c r="M21">
-        <v>0.918</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.04350710900473934</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>-0.06652173913043478</v>
+        <v>0</v>
       </c>
       <c r="P21">
         <v>-0</v>
@@ -2969,52 +2996,58 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0.918</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.55</v>
+        <v>0.944</v>
       </c>
       <c r="V21">
-        <v>0.1208530805687204</v>
+        <v>0.04140350877192982</v>
       </c>
       <c r="W21">
-        <v>-16.08391608391608</v>
+        <v>-0.3551912568306011</v>
       </c>
       <c r="X21">
-        <v>0.07974158532798442</v>
+        <v>0.06779199211714287</v>
       </c>
       <c r="Y21">
-        <v>-16.16365766924407</v>
+        <v>-0.422983248947744</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>-0.4796893440438573</v>
       </c>
       <c r="AB21">
-        <v>0.07952300177083105</v>
+        <v>0.06757585600219319</v>
+      </c>
+      <c r="AC21">
+        <v>-0.5472652000460505</v>
       </c>
       <c r="AD21">
-        <v>0.244</v>
+        <v>0.219</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0.244</v>
+        <v>0.219</v>
       </c>
       <c r="AG21">
-        <v>-2.306</v>
+        <v>-0.725</v>
       </c>
       <c r="AH21">
-        <v>0.01143178410794603</v>
+        <v>0.009513879838394369</v>
       </c>
       <c r="AI21">
-        <v>0.07498463429625078</v>
+        <v>0.00675529781918011</v>
       </c>
       <c r="AJ21">
-        <v>-0.1226987336383952</v>
+        <v>-0.03284258210645526</v>
       </c>
       <c r="AK21">
-        <v>-3.275568181818183</v>
+        <v>-0.02303415409054805</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3023,13 +3056,13 @@
         <v>-0.011</v>
       </c>
       <c r="AN21">
-        <v>-0.3210526315789474</v>
+        <v>-0.008725099601593626</v>
       </c>
       <c r="AP21">
-        <v>3.034210526315789</v>
+        <v>0.02888446215139442</v>
       </c>
       <c r="AQ21">
-        <v>74.45454545454545</v>
+        <v>2290.909090909091</v>
       </c>
     </row>
     <row r="22">
@@ -3040,7 +3073,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spree Acquisition Corp. 1 Limited (NYSE:SHAP)</t>
+          <t>Migdalor- Alternative Products Ltd (TASE:MGDA)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3048,71 +3081,241 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G22">
+        <v>0.2570888468809074</v>
+      </c>
+      <c r="H22">
+        <v>0.2570888468809074</v>
+      </c>
+      <c r="I22">
+        <v>-0.2948960302457467</v>
+      </c>
+      <c r="J22">
+        <v>-0.2948960302457467</v>
+      </c>
       <c r="K22">
-        <v>-0.595</v>
+        <v>-1.57</v>
+      </c>
+      <c r="L22">
+        <v>-0.2967863894139887</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.06352941176470589</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>-0.6878980891719746</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>1.08</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.06352941176470589</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>-0.6878980891719746</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>0.094</v>
+        <v>9.73</v>
       </c>
       <c r="V22">
-        <v>0.0003517964071856288</v>
+        <v>0.5723529411764706</v>
+      </c>
+      <c r="W22">
+        <v>6.108949416342413</v>
       </c>
       <c r="X22">
-        <v>0.07938024802941726</v>
+        <v>0.07210237445805887</v>
+      </c>
+      <c r="Y22">
+        <v>6.036847041884355</v>
+      </c>
+      <c r="Z22">
+        <v>4.727435210008936</v>
+      </c>
+      <c r="AA22">
+        <v>-1.394101876675603</v>
       </c>
       <c r="AB22">
-        <v>0.07938024802941726</v>
+        <v>0.06786900318087519</v>
+      </c>
+      <c r="AC22">
+        <v>-1.461970879856478</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AG22">
-        <v>-0.094</v>
+        <v>-6.26</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>0.1695163654127992</v>
       </c>
       <c r="AI22">
-        <v>-0</v>
+        <v>0.2009264620729589</v>
       </c>
       <c r="AJ22">
-        <v>-0.0003519202114516334</v>
+        <v>-0.5828677839851024</v>
       </c>
       <c r="AK22">
-        <v>0.0105570530098832</v>
+        <v>-0.8302387267904509</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>-0.249</v>
+      </c>
+      <c r="AN22">
+        <v>-2.609022556390977</v>
+      </c>
+      <c r="AO22">
+        <v>-10.90909090909091</v>
+      </c>
+      <c r="AP22">
+        <v>4.706766917293232</v>
+      </c>
+      <c r="AQ22">
+        <v>6.265060240963855</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mia Dynamics Motors Ltd (TASE:MIA)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>-2.48187134502924</v>
+      </c>
+      <c r="H23">
+        <v>-3.625730994152047</v>
+      </c>
+      <c r="I23">
+        <v>-4.912280701754386</v>
+      </c>
+      <c r="J23">
+        <v>-4.912280701754386</v>
+      </c>
+      <c r="K23">
+        <v>-4.24</v>
+      </c>
+      <c r="L23">
+        <v>-4.959064327485381</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0.319</v>
+      </c>
+      <c r="V23">
+        <v>0.01876470588235294</v>
+      </c>
+      <c r="W23">
+        <v>-1.408637873754153</v>
+      </c>
+      <c r="X23">
+        <v>0.06829607924857227</v>
+      </c>
+      <c r="Y23">
+        <v>-1.476933953002725</v>
+      </c>
+      <c r="Z23">
+        <v>1.214488636363637</v>
+      </c>
+      <c r="AA23">
+        <v>-5.965909090909093</v>
+      </c>
+      <c r="AB23">
+        <v>0.0676327279982645</v>
+      </c>
+      <c r="AC23">
+        <v>-6.033541818907358</v>
+      </c>
+      <c r="AD23">
+        <v>0.55</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0.55</v>
+      </c>
+      <c r="AG23">
+        <v>0.231</v>
+      </c>
+      <c r="AH23">
+        <v>0.03133903133903134</v>
+      </c>
+      <c r="AI23">
+        <v>1.02803738317757</v>
+      </c>
+      <c r="AJ23">
+        <v>0.01340607045441356</v>
+      </c>
+      <c r="AK23">
+        <v>1.069444444444444</v>
+      </c>
+      <c r="AL23">
+        <v>0.037</v>
+      </c>
+      <c r="AM23">
+        <v>0.036</v>
+      </c>
+      <c r="AN23">
+        <v>-0.1325301204819277</v>
+      </c>
+      <c r="AO23">
+        <v>-113.5135135135135</v>
+      </c>
+      <c r="AP23">
+        <v>-0.05566265060240964</v>
+      </c>
+      <c r="AQ23">
+        <v>-116.6666666666667</v>
       </c>
     </row>
   </sheetData>
